--- a/research/traditional_assets/database/data/norway/norway_farming_agriculture.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_farming_agriculture.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07129124021041604</v>
+        <v>0.07116949948195311</v>
       </c>
       <c r="C2">
-        <v>326.3988292507786</v>
+        <v>324.2853414744593</v>
       </c>
       <c r="D2">
-        <v>310.3988292507786</v>
+        <v>311.8883414744593</v>
       </c>
       <c r="E2">
-        <v>-143</v>
+        <v>-139.397</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3.603</v>
       </c>
       <c r="G2">
         <v>16</v>
@@ -1451,28 +1451,28 @@
         <v>13.1</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1812309</v>
       </c>
       <c r="N2">
-        <v>13.1</v>
+        <v>12.9187691</v>
       </c>
       <c r="O2">
-        <v>2.882</v>
+        <v>2.842129202</v>
       </c>
       <c r="P2">
-        <v>10.218</v>
+        <v>10.076639898</v>
       </c>
       <c r="Q2">
-        <v>28.61799999999999</v>
+        <v>28.476639898</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07129124021041604</v>
+        <v>0.07149208028480113</v>
       </c>
       <c r="T2">
-        <v>0.5887122450442503</v>
+        <v>0.5933505839445989</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>72.28347925215843</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07116949948195311</v>
+        <v>0.07104775875349019</v>
       </c>
       <c r="C3">
-        <v>324.2853414744593</v>
+        <v>322.1862180862772</v>
       </c>
       <c r="D3">
-        <v>311.8883414744593</v>
+        <v>313.3922180862772</v>
       </c>
       <c r="E3">
-        <v>-139.397</v>
+        <v>-135.794</v>
       </c>
       <c r="F3">
-        <v>3.603</v>
+        <v>7.206</v>
       </c>
       <c r="G3">
         <v>16</v>
@@ -1533,28 +1533,28 @@
         <v>13.1</v>
       </c>
       <c r="M3">
-        <v>0.1812309</v>
+        <v>0.3624618</v>
       </c>
       <c r="N3">
-        <v>12.9187691</v>
+        <v>12.7375382</v>
       </c>
       <c r="O3">
-        <v>2.842129202</v>
+        <v>2.802258403999999</v>
       </c>
       <c r="P3">
-        <v>10.076639898</v>
+        <v>9.935279795999998</v>
       </c>
       <c r="Q3">
-        <v>28.476639898</v>
+        <v>28.33527979599999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07149208028480113</v>
+        <v>0.07169701913621448</v>
       </c>
       <c r="T3">
-        <v>0.5933505839445989</v>
+        <v>0.5980835828225057</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>72.28347925215843</v>
+        <v>36.14173962607921</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07104775875349019</v>
+        <v>0.07092601802502729</v>
       </c>
       <c r="C4">
-        <v>322.1862180862772</v>
+        <v>320.1016678814824</v>
       </c>
       <c r="D4">
-        <v>313.3922180862772</v>
+        <v>314.9106678814824</v>
       </c>
       <c r="E4">
-        <v>-135.794</v>
+        <v>-132.191</v>
       </c>
       <c r="F4">
-        <v>7.206</v>
+        <v>10.809</v>
       </c>
       <c r="G4">
         <v>16</v>
@@ -1615,28 +1615,28 @@
         <v>13.1</v>
       </c>
       <c r="M4">
-        <v>0.3624618</v>
+        <v>0.5436926999999999</v>
       </c>
       <c r="N4">
-        <v>12.7375382</v>
+        <v>12.5563073</v>
       </c>
       <c r="O4">
-        <v>2.802258403999999</v>
+        <v>2.762387606</v>
       </c>
       <c r="P4">
-        <v>9.935279795999998</v>
+        <v>9.793919694</v>
       </c>
       <c r="Q4">
-        <v>28.33527979599999</v>
+        <v>28.193919694</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07169701913621448</v>
+        <v>0.07190618353095597</v>
       </c>
       <c r="T4">
-        <v>0.5980835828225057</v>
+        <v>0.6029141693061426</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>36.14173962607921</v>
+        <v>24.09449308405281</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07092601802502729</v>
+        <v>0.07080427729656437</v>
       </c>
       <c r="C5">
-        <v>320.1016678814824</v>
+        <v>318.0319037216523</v>
       </c>
       <c r="D5">
-        <v>314.9106678814824</v>
+        <v>316.4439037216522</v>
       </c>
       <c r="E5">
-        <v>-132.191</v>
+        <v>-128.588</v>
       </c>
       <c r="F5">
-        <v>10.809</v>
+        <v>14.412</v>
       </c>
       <c r="G5">
         <v>16</v>
@@ -1697,28 +1697,28 @@
         <v>13.1</v>
       </c>
       <c r="M5">
-        <v>0.5436926999999999</v>
+        <v>0.7249236</v>
       </c>
       <c r="N5">
-        <v>12.5563073</v>
+        <v>12.3750764</v>
       </c>
       <c r="O5">
-        <v>2.762387606</v>
+        <v>2.722516808</v>
       </c>
       <c r="P5">
-        <v>9.793919694</v>
+        <v>9.652559591999998</v>
       </c>
       <c r="Q5">
-        <v>28.193919694</v>
+        <v>28.05255959199999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07190618353095597</v>
+        <v>0.07211970551725455</v>
       </c>
       <c r="T5">
-        <v>0.6029141693061426</v>
+        <v>0.6078453930081885</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>24.09449308405281</v>
+        <v>18.0708698130396</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07080427729656437</v>
+        <v>0.07068253656810145</v>
       </c>
       <c r="C6">
-        <v>318.0319037216523</v>
+        <v>315.9771426341638</v>
       </c>
       <c r="D6">
-        <v>316.4439037216522</v>
+        <v>317.9921426341638</v>
       </c>
       <c r="E6">
-        <v>-128.588</v>
+        <v>-124.985</v>
       </c>
       <c r="F6">
-        <v>14.412</v>
+        <v>18.015</v>
       </c>
       <c r="G6">
         <v>16</v>
@@ -1779,28 +1779,28 @@
         <v>13.1</v>
       </c>
       <c r="M6">
-        <v>0.7249236</v>
+        <v>0.9061545</v>
       </c>
       <c r="N6">
-        <v>12.3750764</v>
+        <v>12.1938455</v>
       </c>
       <c r="O6">
-        <v>2.722516808</v>
+        <v>2.68264601</v>
       </c>
       <c r="P6">
-        <v>9.652559591999998</v>
+        <v>9.511199489999999</v>
       </c>
       <c r="Q6">
-        <v>28.05255959199999</v>
+        <v>27.91119949</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07211970551725455</v>
+        <v>0.07233772270326469</v>
       </c>
       <c r="T6">
-        <v>0.6078453930081885</v>
+        <v>0.612880431946067</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>18.0708698130396</v>
+        <v>14.45669585043169</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07068253656810145</v>
+        <v>0.07063099583963854</v>
       </c>
       <c r="C7">
-        <v>315.9771426341638</v>
+        <v>313.0341865076633</v>
       </c>
       <c r="D7">
-        <v>317.9921426341638</v>
+        <v>318.6521865076633</v>
       </c>
       <c r="E7">
-        <v>-124.985</v>
+        <v>-121.382</v>
       </c>
       <c r="F7">
-        <v>18.015</v>
+        <v>21.618</v>
       </c>
       <c r="G7">
         <v>16</v>
@@ -1861,45 +1861,45 @@
         <v>13.1</v>
       </c>
       <c r="M7">
-        <v>0.9061545</v>
+        <v>1.1198124</v>
       </c>
       <c r="N7">
-        <v>12.1938455</v>
+        <v>11.9801876</v>
       </c>
       <c r="O7">
-        <v>2.68264601</v>
+        <v>2.635641272</v>
       </c>
       <c r="P7">
-        <v>9.511199489999999</v>
+        <v>9.344546327999998</v>
       </c>
       <c r="Q7">
-        <v>27.91119949</v>
+        <v>27.744546328</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07233772270326469</v>
+        <v>0.07256037855280696</v>
       </c>
       <c r="T7">
-        <v>0.612880431946067</v>
+        <v>0.6180225993719853</v>
       </c>
       <c r="U7">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V7">
         <v>0.22</v>
       </c>
       <c r="W7">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y7">
-        <v>14.45669585043169</v>
+        <v>11.69838805142718</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07063099583963854</v>
+        <v>0.07052095511117563</v>
       </c>
       <c r="C8">
-        <v>313.0341865076633</v>
+        <v>310.8496073806396</v>
       </c>
       <c r="D8">
-        <v>318.6521865076633</v>
+        <v>320.0706073806396</v>
       </c>
       <c r="E8">
-        <v>-121.382</v>
+        <v>-117.779</v>
       </c>
       <c r="F8">
-        <v>21.618</v>
+        <v>25.221</v>
       </c>
       <c r="G8">
         <v>16</v>
@@ -1943,28 +1943,28 @@
         <v>13.1</v>
       </c>
       <c r="M8">
-        <v>1.1198124</v>
+        <v>1.3064478</v>
       </c>
       <c r="N8">
-        <v>11.9801876</v>
+        <v>11.7935522</v>
       </c>
       <c r="O8">
-        <v>2.635641272</v>
+        <v>2.594581484</v>
       </c>
       <c r="P8">
-        <v>9.344546327999998</v>
+        <v>9.198970715999998</v>
       </c>
       <c r="Q8">
-        <v>27.744546328</v>
+        <v>27.598970716</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07256037855280696</v>
+        <v>0.07278782270018885</v>
       </c>
       <c r="T8">
-        <v>0.6180225993719853</v>
+        <v>0.6232753510436224</v>
       </c>
       <c r="U8">
         <v>0.0518</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>11.69838805142718</v>
+        <v>10.02718975836616</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07052095511117563</v>
+        <v>0.07051699438271272</v>
       </c>
       <c r="C9">
-        <v>310.8496073806396</v>
+        <v>307.2978964955362</v>
       </c>
       <c r="D9">
-        <v>320.0706073806396</v>
+        <v>320.1218964955362</v>
       </c>
       <c r="E9">
-        <v>-117.779</v>
+        <v>-114.176</v>
       </c>
       <c r="F9">
-        <v>25.221</v>
+        <v>28.824</v>
       </c>
       <c r="G9">
         <v>16</v>
@@ -2025,45 +2025,45 @@
         <v>13.1</v>
       </c>
       <c r="M9">
-        <v>1.3064478</v>
+        <v>1.542084</v>
       </c>
       <c r="N9">
-        <v>11.7935522</v>
+        <v>11.557916</v>
       </c>
       <c r="O9">
-        <v>2.594581483999999</v>
+        <v>2.54274152</v>
       </c>
       <c r="P9">
-        <v>9.198970715999998</v>
+        <v>9.015174479999999</v>
       </c>
       <c r="Q9">
-        <v>27.598970716</v>
+        <v>27.41517448</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07278782270018885</v>
+        <v>0.0730202112855573</v>
       </c>
       <c r="T9">
-        <v>0.6232753510436225</v>
+        <v>0.6286422929689908</v>
       </c>
       <c r="U9">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V9">
         <v>0.22</v>
       </c>
       <c r="W9">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y9">
-        <v>10.02718975836616</v>
+        <v>8.494997678466284</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07051699438271272</v>
+        <v>0.0704763736542498</v>
       </c>
       <c r="C10">
-        <v>307.2978964955362</v>
+        <v>304.2218614708108</v>
       </c>
       <c r="D10">
-        <v>320.1218964955362</v>
+        <v>320.6488614708108</v>
       </c>
       <c r="E10">
-        <v>-114.176</v>
+        <v>-110.573</v>
       </c>
       <c r="F10">
-        <v>28.824</v>
+        <v>32.427</v>
       </c>
       <c r="G10">
         <v>16</v>
@@ -2107,45 +2107,45 @@
         <v>13.1</v>
       </c>
       <c r="M10">
-        <v>1.542084</v>
+        <v>1.7607861</v>
       </c>
       <c r="N10">
-        <v>11.557916</v>
+        <v>11.3392139</v>
       </c>
       <c r="O10">
-        <v>2.54274152</v>
+        <v>2.494627057999999</v>
       </c>
       <c r="P10">
-        <v>9.015174479999999</v>
+        <v>8.844586841999998</v>
       </c>
       <c r="Q10">
-        <v>27.41517448</v>
+        <v>27.244586842</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.0730202112855573</v>
+        <v>0.07325770731236242</v>
       </c>
       <c r="T10">
-        <v>0.6286422929689908</v>
+        <v>0.6341271896619497</v>
       </c>
       <c r="U10">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V10">
         <v>0.22</v>
       </c>
       <c r="W10">
-        <v>0.04173</v>
+        <v>0.042354</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y10">
-        <v>8.494997678466284</v>
+        <v>7.439858822147674</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0704763736542498</v>
+        <v>0.07038583292578689</v>
       </c>
       <c r="C11">
-        <v>304.2218614708108</v>
+        <v>301.7996952292605</v>
       </c>
       <c r="D11">
-        <v>320.6488614708108</v>
+        <v>321.8296952292604</v>
       </c>
       <c r="E11">
-        <v>-110.573</v>
+        <v>-106.97</v>
       </c>
       <c r="F11">
-        <v>32.427</v>
+        <v>36.03</v>
       </c>
       <c r="G11">
         <v>16</v>
@@ -2189,28 +2189,28 @@
         <v>13.1</v>
       </c>
       <c r="M11">
-        <v>1.7607861</v>
+        <v>1.956429</v>
       </c>
       <c r="N11">
-        <v>11.3392139</v>
+        <v>11.143571</v>
       </c>
       <c r="O11">
-        <v>2.494627057999999</v>
+        <v>2.451585619999999</v>
       </c>
       <c r="P11">
-        <v>8.844586841999998</v>
+        <v>8.691985379999998</v>
       </c>
       <c r="Q11">
-        <v>27.244586842</v>
+        <v>27.09198538</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07325770731236242</v>
+        <v>0.07350048102865209</v>
       </c>
       <c r="T11">
-        <v>0.6341271896619497</v>
+        <v>0.6397339729480854</v>
       </c>
       <c r="U11">
         <v>0.0543</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>7.439858822147674</v>
+        <v>6.695872939932907</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07038583292578689</v>
+        <v>0.07038109219732397</v>
       </c>
       <c r="C12">
-        <v>301.7996952292605</v>
+        <v>298.2587635533259</v>
       </c>
       <c r="D12">
-        <v>321.8296952292604</v>
+        <v>321.8917635533259</v>
       </c>
       <c r="E12">
-        <v>-106.97</v>
+        <v>-103.367</v>
       </c>
       <c r="F12">
-        <v>36.03</v>
+        <v>39.633</v>
       </c>
       <c r="G12">
         <v>16</v>
@@ -2271,45 +2271,45 @@
         <v>13.1</v>
       </c>
       <c r="M12">
-        <v>1.956429</v>
+        <v>2.1917049</v>
       </c>
       <c r="N12">
-        <v>11.143571</v>
+        <v>10.9082951</v>
       </c>
       <c r="O12">
-        <v>2.451585619999999</v>
+        <v>2.399824921999999</v>
       </c>
       <c r="P12">
-        <v>8.691985379999998</v>
+        <v>8.508470177999998</v>
       </c>
       <c r="Q12">
-        <v>27.09198538</v>
+        <v>26.90847017799999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07350048102865209</v>
+        <v>0.07374871033407188</v>
       </c>
       <c r="T12">
-        <v>0.6397339729480854</v>
+        <v>0.6454667513642467</v>
       </c>
       <c r="U12">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V12">
         <v>0.22</v>
       </c>
       <c r="W12">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y12">
-        <v>6.695872939932907</v>
+        <v>5.97708204238627</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07038109219732397</v>
+        <v>0.07029835146886106</v>
       </c>
       <c r="C13">
-        <v>298.2587635533259</v>
+        <v>295.7429207457789</v>
       </c>
       <c r="D13">
-        <v>321.8917635533259</v>
+        <v>322.9789207457789</v>
       </c>
       <c r="E13">
-        <v>-103.367</v>
+        <v>-99.76400000000001</v>
       </c>
       <c r="F13">
-        <v>39.633</v>
+        <v>43.236</v>
       </c>
       <c r="G13">
         <v>16</v>
@@ -2353,28 +2353,28 @@
         <v>13.1</v>
       </c>
       <c r="M13">
-        <v>2.1917049</v>
+        <v>2.3909508</v>
       </c>
       <c r="N13">
-        <v>10.9082951</v>
+        <v>10.7090492</v>
       </c>
       <c r="O13">
-        <v>2.399824921999999</v>
+        <v>2.355990824</v>
       </c>
       <c r="P13">
-        <v>8.508470177999998</v>
+        <v>8.353058376</v>
       </c>
       <c r="Q13">
-        <v>26.90847017799999</v>
+        <v>26.753058376</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07374871033407188</v>
+        <v>0.07400258121461484</v>
       </c>
       <c r="T13">
-        <v>0.6454667513642467</v>
+        <v>0.651329820198957</v>
       </c>
       <c r="U13">
         <v>0.0553</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>5.97708204238627</v>
+        <v>5.478991872187416</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07029835146886106</v>
+        <v>0.07021561074039814</v>
       </c>
       <c r="C14">
-        <v>295.7429207457789</v>
+        <v>293.2344463533835</v>
       </c>
       <c r="D14">
-        <v>322.9789207457789</v>
+        <v>324.0734463533835</v>
       </c>
       <c r="E14">
-        <v>-99.76400000000001</v>
+        <v>-96.161</v>
       </c>
       <c r="F14">
-        <v>43.236</v>
+        <v>46.83900000000001</v>
       </c>
       <c r="G14">
         <v>16</v>
@@ -2435,28 +2435,28 @@
         <v>13.1</v>
       </c>
       <c r="M14">
-        <v>2.3909508</v>
+        <v>2.5901967</v>
       </c>
       <c r="N14">
-        <v>10.7090492</v>
+        <v>10.5098033</v>
       </c>
       <c r="O14">
-        <v>2.355990824</v>
+        <v>2.312156726</v>
       </c>
       <c r="P14">
-        <v>8.353058376</v>
+        <v>8.197646573999998</v>
       </c>
       <c r="Q14">
-        <v>26.753058376</v>
+        <v>26.597646574</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07400258121461484</v>
+        <v>0.07426228820735419</v>
       </c>
       <c r="T14">
-        <v>0.651329820198957</v>
+        <v>0.6573276722252699</v>
       </c>
       <c r="U14">
         <v>0.0553</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>5.478991872187416</v>
+        <v>5.057530958942229</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07021561074039814</v>
+        <v>0.07013287001193523</v>
       </c>
       <c r="C15">
-        <v>293.2344463533835</v>
+        <v>290.7334155421233</v>
       </c>
       <c r="D15">
-        <v>324.0734463533835</v>
+        <v>325.1754155421233</v>
       </c>
       <c r="E15">
-        <v>-96.161</v>
+        <v>-92.55799999999999</v>
       </c>
       <c r="F15">
-        <v>46.83900000000001</v>
+        <v>50.44200000000001</v>
       </c>
       <c r="G15">
         <v>16</v>
@@ -2517,28 +2517,28 @@
         <v>13.1</v>
       </c>
       <c r="M15">
-        <v>2.5901967</v>
+        <v>2.789442600000001</v>
       </c>
       <c r="N15">
-        <v>10.5098033</v>
+        <v>10.3105574</v>
       </c>
       <c r="O15">
-        <v>2.312156726</v>
+        <v>2.268322628</v>
       </c>
       <c r="P15">
-        <v>8.197646573999998</v>
+        <v>8.042234771999997</v>
       </c>
       <c r="Q15">
-        <v>26.597646574</v>
+        <v>26.442234772</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07426228820735419</v>
+        <v>0.0745280348975991</v>
       </c>
       <c r="T15">
-        <v>0.6573276722252699</v>
+        <v>0.6634650091824272</v>
       </c>
       <c r="U15">
         <v>0.0553</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>5.057530958942229</v>
+        <v>4.696278747589211</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07013287001193523</v>
+        <v>0.0703426292834723</v>
       </c>
       <c r="C16">
-        <v>290.7334155421233</v>
+        <v>284.3512284591886</v>
       </c>
       <c r="D16">
-        <v>325.1754155421233</v>
+        <v>322.3962284591886</v>
       </c>
       <c r="E16">
-        <v>-92.55799999999999</v>
+        <v>-88.95499999999998</v>
       </c>
       <c r="F16">
-        <v>50.44200000000001</v>
+        <v>54.04500000000001</v>
       </c>
       <c r="G16">
         <v>16</v>
@@ -2599,45 +2599,45 @@
         <v>13.1</v>
       </c>
       <c r="M16">
-        <v>2.789442600000001</v>
+        <v>3.123801000000001</v>
       </c>
       <c r="N16">
-        <v>10.3105574</v>
+        <v>9.976198999999998</v>
       </c>
       <c r="O16">
-        <v>2.268322628</v>
+        <v>2.194763779999999</v>
       </c>
       <c r="P16">
-        <v>8.042234771999997</v>
+        <v>7.781435219999999</v>
       </c>
       <c r="Q16">
-        <v>26.442234772</v>
+        <v>26.18143522</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.0745280348975991</v>
+        <v>0.07480003445114389</v>
       </c>
       <c r="T16">
-        <v>0.6634650091824272</v>
+        <v>0.6697467540679883</v>
       </c>
       <c r="U16">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V16">
         <v>0.22</v>
       </c>
       <c r="W16">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y16">
-        <v>4.696278747589211</v>
+        <v>4.193609003902615</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07034262928347229</v>
+        <v>0.07071618855500938</v>
       </c>
       <c r="C17">
-        <v>284.3512284591888</v>
+        <v>275.9146601153136</v>
       </c>
       <c r="D17">
-        <v>322.3962284591888</v>
+        <v>317.5626601153136</v>
       </c>
       <c r="E17">
-        <v>-88.955</v>
+        <v>-85.352</v>
       </c>
       <c r="F17">
-        <v>54.045</v>
+        <v>57.648</v>
       </c>
       <c r="G17">
         <v>16</v>
@@ -2681,45 +2681,45 @@
         <v>13.1</v>
       </c>
       <c r="M17">
-        <v>3.123801</v>
+        <v>3.5338224</v>
       </c>
       <c r="N17">
-        <v>9.976198999999998</v>
+        <v>9.566177599999998</v>
       </c>
       <c r="O17">
-        <v>2.194763779999999</v>
+        <v>2.104559071999999</v>
       </c>
       <c r="P17">
-        <v>7.781435219999999</v>
+        <v>7.461618527999999</v>
       </c>
       <c r="Q17">
-        <v>26.18143522</v>
+        <v>25.861618528</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07480003445114389</v>
+        <v>0.07507851018453499</v>
       </c>
       <c r="T17">
-        <v>0.6697467540679883</v>
+        <v>0.6761780643079676</v>
       </c>
       <c r="U17">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V17">
         <v>0.22</v>
       </c>
       <c r="W17">
-        <v>0.04508400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y17">
-        <v>4.193609003902616</v>
+        <v>3.707034060342138</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07071618855500938</v>
+        <v>0.07105152782654649</v>
       </c>
       <c r="C18">
-        <v>275.9146601153136</v>
+        <v>268.0944407913207</v>
       </c>
       <c r="D18">
-        <v>317.5626601153136</v>
+        <v>313.3454407913208</v>
       </c>
       <c r="E18">
-        <v>-85.352</v>
+        <v>-81.749</v>
       </c>
       <c r="F18">
-        <v>57.648</v>
+        <v>61.251</v>
       </c>
       <c r="G18">
         <v>16</v>
@@ -2763,45 +2763,45 @@
         <v>13.1</v>
       </c>
       <c r="M18">
-        <v>3.5338224</v>
+        <v>3.926189100000001</v>
       </c>
       <c r="N18">
-        <v>9.566177599999998</v>
+        <v>9.173810899999998</v>
       </c>
       <c r="O18">
-        <v>2.104559071999999</v>
+        <v>2.018238397999999</v>
       </c>
       <c r="P18">
-        <v>7.461618527999999</v>
+        <v>7.155572501999998</v>
       </c>
       <c r="Q18">
-        <v>25.861618528</v>
+        <v>25.555572502</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07507851018453499</v>
+        <v>0.07536369617656202</v>
       </c>
       <c r="T18">
-        <v>0.6761780643079676</v>
+        <v>0.6827643458790307</v>
       </c>
       <c r="U18">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V18">
         <v>0.22</v>
       </c>
       <c r="W18">
-        <v>0.047814</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y18">
-        <v>3.707034060342138</v>
+        <v>3.336568786256372</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07105152782654649</v>
+        <v>0.07103742709808356</v>
       </c>
       <c r="C19">
-        <v>268.0944407913207</v>
+        <v>264.6665140647779</v>
       </c>
       <c r="D19">
-        <v>313.3454407913208</v>
+        <v>313.5205140647778</v>
       </c>
       <c r="E19">
-        <v>-81.749</v>
+        <v>-78.14599999999999</v>
       </c>
       <c r="F19">
-        <v>61.251</v>
+        <v>64.85400000000001</v>
       </c>
       <c r="G19">
         <v>16</v>
@@ -2845,28 +2845,28 @@
         <v>13.1</v>
       </c>
       <c r="M19">
-        <v>3.926189100000001</v>
+        <v>4.157141400000001</v>
       </c>
       <c r="N19">
-        <v>9.173810899999998</v>
+        <v>8.942858599999997</v>
       </c>
       <c r="O19">
-        <v>2.018238397999999</v>
+        <v>1.967428891999999</v>
       </c>
       <c r="P19">
-        <v>7.155572501999998</v>
+        <v>6.975429707999998</v>
       </c>
       <c r="Q19">
-        <v>25.555572502</v>
+        <v>25.375429708</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07536369617656202</v>
+        <v>0.07565583792449215</v>
       </c>
       <c r="T19">
-        <v>0.6827643458790307</v>
+        <v>0.6895112684640221</v>
       </c>
       <c r="U19">
         <v>0.0641</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>3.336568786256372</v>
+        <v>3.151203853686573</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07103742709808357</v>
+        <v>0.07217928636962065</v>
       </c>
       <c r="C20">
-        <v>264.6665140647777</v>
+        <v>247.4923999419097</v>
       </c>
       <c r="D20">
-        <v>313.5205140647777</v>
+        <v>299.9493999419097</v>
       </c>
       <c r="E20">
-        <v>-78.146</v>
+        <v>-74.54299999999999</v>
       </c>
       <c r="F20">
-        <v>64.854</v>
+        <v>68.45700000000001</v>
       </c>
       <c r="G20">
         <v>16</v>
@@ -2927,45 +2927,45 @@
         <v>13.1</v>
       </c>
       <c r="M20">
-        <v>4.1571414</v>
+        <v>4.922058300000001</v>
       </c>
       <c r="N20">
-        <v>8.942858599999997</v>
+        <v>8.177941699999998</v>
       </c>
       <c r="O20">
-        <v>1.967428891999999</v>
+        <v>1.799147174</v>
       </c>
       <c r="P20">
-        <v>6.975429707999998</v>
+        <v>6.378794525999998</v>
       </c>
       <c r="Q20">
-        <v>25.375429708</v>
+        <v>24.778794526</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07565583792449215</v>
+        <v>0.07595519304891438</v>
       </c>
       <c r="T20">
-        <v>0.689511268464022</v>
+        <v>0.6964247817301243</v>
       </c>
       <c r="U20">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V20">
         <v>0.22</v>
       </c>
       <c r="W20">
-        <v>0.04999800000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>3.151203853686573</v>
+        <v>2.661488182697876</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07217928636962065</v>
+        <v>0.07222602564115774</v>
       </c>
       <c r="C21">
-        <v>247.4923999419097</v>
+        <v>243.3588844326294</v>
       </c>
       <c r="D21">
-        <v>299.9493999419097</v>
+        <v>299.4188844326294</v>
       </c>
       <c r="E21">
-        <v>-74.54299999999999</v>
+        <v>-70.94</v>
       </c>
       <c r="F21">
-        <v>68.45700000000001</v>
+        <v>72.06</v>
       </c>
       <c r="G21">
         <v>16</v>
@@ -3009,28 +3009,28 @@
         <v>13.1</v>
       </c>
       <c r="M21">
-        <v>4.922058300000001</v>
+        <v>5.181114000000001</v>
       </c>
       <c r="N21">
-        <v>8.177941699999998</v>
+        <v>7.918885999999997</v>
       </c>
       <c r="O21">
-        <v>1.799147174</v>
+        <v>1.742154919999999</v>
       </c>
       <c r="P21">
-        <v>6.378794525999998</v>
+        <v>6.176731079999998</v>
       </c>
       <c r="Q21">
-        <v>24.778794526</v>
+        <v>24.57673107999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07595519304891438</v>
+        <v>0.07626203205144716</v>
       </c>
       <c r="T21">
-        <v>0.6964247817301243</v>
+        <v>0.7035111328278792</v>
       </c>
       <c r="U21">
         <v>0.07190000000000001</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>2.661488182697876</v>
+        <v>2.528413773562982</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07222602564115774</v>
+        <v>0.07291158491269481</v>
       </c>
       <c r="C22">
-        <v>243.3588844326294</v>
+        <v>232.1846047395724</v>
       </c>
       <c r="D22">
-        <v>299.4188844326294</v>
+        <v>291.8476047395724</v>
       </c>
       <c r="E22">
-        <v>-70.94</v>
+        <v>-67.33699999999999</v>
       </c>
       <c r="F22">
-        <v>72.06</v>
+        <v>75.66300000000001</v>
       </c>
       <c r="G22">
         <v>16</v>
@@ -3091,45 +3091,45 @@
         <v>13.1</v>
       </c>
       <c r="M22">
-        <v>5.181114000000001</v>
+        <v>5.735255400000002</v>
       </c>
       <c r="N22">
-        <v>7.918885999999997</v>
+        <v>7.364744599999996</v>
       </c>
       <c r="O22">
-        <v>1.742154919999999</v>
+        <v>1.620243811999999</v>
       </c>
       <c r="P22">
-        <v>6.176731079999998</v>
+        <v>5.744500787999997</v>
       </c>
       <c r="Q22">
-        <v>24.57673107999999</v>
+        <v>24.14450078799999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07626203205144716</v>
+        <v>0.07657663912999343</v>
       </c>
       <c r="T22">
-        <v>0.7035111328278792</v>
+        <v>0.7107768852192482</v>
       </c>
       <c r="U22">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V22">
         <v>0.22</v>
       </c>
       <c r="W22">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y22">
-        <v>2.528413773562982</v>
+        <v>2.284117983655967</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07291158491269481</v>
+        <v>0.0729887441842319</v>
       </c>
       <c r="C23">
-        <v>232.1846047395724</v>
+        <v>227.753366832409</v>
       </c>
       <c r="D23">
-        <v>291.8476047395724</v>
+        <v>291.019366832409</v>
       </c>
       <c r="E23">
-        <v>-67.337</v>
+        <v>-63.73399999999999</v>
       </c>
       <c r="F23">
-        <v>75.663</v>
+        <v>79.26600000000001</v>
       </c>
       <c r="G23">
         <v>16</v>
@@ -3173,28 +3173,28 @@
         <v>13.1</v>
       </c>
       <c r="M23">
-        <v>5.7352554</v>
+        <v>6.008362800000001</v>
       </c>
       <c r="N23">
-        <v>7.364744599999998</v>
+        <v>7.091637199999997</v>
       </c>
       <c r="O23">
-        <v>1.620243812</v>
+        <v>1.560160183999999</v>
       </c>
       <c r="P23">
-        <v>5.744500787999998</v>
+        <v>5.531477015999998</v>
       </c>
       <c r="Q23">
-        <v>24.14450078799999</v>
+        <v>23.931477016</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07657663912999343</v>
+        <v>0.07689931305670757</v>
       </c>
       <c r="T23">
-        <v>0.710776885219248</v>
+        <v>0.7182289389539854</v>
       </c>
       <c r="U23">
         <v>0.07580000000000001</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>2.284117983655968</v>
+        <v>2.180294438944332</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.0729887441842319</v>
+        <v>0.07306590345576899</v>
       </c>
       <c r="C24">
-        <v>227.753366832409</v>
+        <v>223.3268165552505</v>
       </c>
       <c r="D24">
-        <v>291.019366832409</v>
+        <v>290.1958165552505</v>
       </c>
       <c r="E24">
-        <v>-63.73399999999999</v>
+        <v>-60.131</v>
       </c>
       <c r="F24">
-        <v>79.26600000000001</v>
+        <v>82.869</v>
       </c>
       <c r="G24">
         <v>16</v>
@@ -3255,28 +3255,28 @@
         <v>13.1</v>
       </c>
       <c r="M24">
-        <v>6.008362800000001</v>
+        <v>6.2814702</v>
       </c>
       <c r="N24">
-        <v>7.091637199999997</v>
+        <v>6.818529799999998</v>
       </c>
       <c r="O24">
-        <v>1.560160183999999</v>
+        <v>1.500076556</v>
       </c>
       <c r="P24">
-        <v>5.531477015999998</v>
+        <v>5.318453243999998</v>
       </c>
       <c r="Q24">
-        <v>23.931477016</v>
+        <v>23.718453244</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07689931305670757</v>
+        <v>0.07723036812437531</v>
       </c>
       <c r="T24">
-        <v>0.7182289389539854</v>
+        <v>0.7258745525259888</v>
       </c>
       <c r="U24">
         <v>0.07580000000000001</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>2.180294438944332</v>
+        <v>2.085499028555448</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07306590345576899</v>
+        <v>0.07580130272730608</v>
       </c>
       <c r="C25">
-        <v>223.3268165552505</v>
+        <v>193.2649180059601</v>
       </c>
       <c r="D25">
-        <v>290.1958165552505</v>
+        <v>263.7369180059601</v>
       </c>
       <c r="E25">
-        <v>-60.131</v>
+        <v>-56.52799999999999</v>
       </c>
       <c r="F25">
-        <v>82.869</v>
+        <v>86.47200000000001</v>
       </c>
       <c r="G25">
         <v>16</v>
@@ -3337,45 +3337,45 @@
         <v>13.1</v>
       </c>
       <c r="M25">
-        <v>6.2814702</v>
+        <v>7.782480000000001</v>
       </c>
       <c r="N25">
-        <v>6.818529799999998</v>
+        <v>5.317519999999997</v>
       </c>
       <c r="O25">
-        <v>1.500076556</v>
+        <v>1.1698544</v>
       </c>
       <c r="P25">
-        <v>5.318453243999998</v>
+        <v>4.147665599999998</v>
       </c>
       <c r="Q25">
-        <v>23.718453244</v>
+        <v>22.54766559999999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07723036812437531</v>
+        <v>0.07757013516750799</v>
       </c>
       <c r="T25">
-        <v>0.7258745525259888</v>
+        <v>0.73372136645515</v>
       </c>
       <c r="U25">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V25">
         <v>0.22</v>
       </c>
       <c r="W25">
-        <v>0.05912400000000001</v>
+        <v>0.0702</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y25">
-        <v>2.085499028555448</v>
+        <v>1.683268058510911</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07580130272730608</v>
+        <v>0.07598922199884316</v>
       </c>
       <c r="C26">
-        <v>193.2649180059601</v>
+        <v>188.0202311313857</v>
       </c>
       <c r="D26">
-        <v>263.7369180059601</v>
+        <v>262.0952311313857</v>
       </c>
       <c r="E26">
-        <v>-56.52800000000001</v>
+        <v>-52.925</v>
       </c>
       <c r="F26">
-        <v>86.47199999999999</v>
+        <v>90.075</v>
       </c>
       <c r="G26">
         <v>16</v>
@@ -3419,28 +3419,28 @@
         <v>13.1</v>
       </c>
       <c r="M26">
-        <v>7.78248</v>
+        <v>8.10675</v>
       </c>
       <c r="N26">
-        <v>5.317519999999998</v>
+        <v>4.993249999999998</v>
       </c>
       <c r="O26">
-        <v>1.1698544</v>
+        <v>1.098514999999999</v>
       </c>
       <c r="P26">
-        <v>4.147665599999999</v>
+        <v>3.894734999999999</v>
       </c>
       <c r="Q26">
-        <v>22.5476656</v>
+        <v>22.294735</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07757013516750799</v>
+        <v>0.07791896266512421</v>
       </c>
       <c r="T26">
-        <v>0.73372136645515</v>
+        <v>0.7417774287557555</v>
       </c>
       <c r="U26">
         <v>0.09</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>1.683268058510912</v>
+        <v>1.615937336170475</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07598922199884316</v>
+        <v>0.07617714127038024</v>
       </c>
       <c r="C27">
-        <v>188.0202311313857</v>
+        <v>182.7958558851384</v>
       </c>
       <c r="D27">
-        <v>262.0952311313857</v>
+        <v>260.4738558851384</v>
       </c>
       <c r="E27">
-        <v>-52.925</v>
+        <v>-49.32199999999999</v>
       </c>
       <c r="F27">
-        <v>90.075</v>
+        <v>93.67800000000001</v>
       </c>
       <c r="G27">
         <v>16</v>
@@ -3501,28 +3501,28 @@
         <v>13.1</v>
       </c>
       <c r="M27">
-        <v>8.10675</v>
+        <v>8.43102</v>
       </c>
       <c r="N27">
-        <v>4.993249999999998</v>
+        <v>4.668979999999998</v>
       </c>
       <c r="O27">
-        <v>1.098514999999999</v>
+        <v>1.027175599999999</v>
       </c>
       <c r="P27">
-        <v>3.894734999999999</v>
+        <v>3.641804399999998</v>
       </c>
       <c r="Q27">
-        <v>22.294735</v>
+        <v>22.0418044</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07791896266512421</v>
+        <v>0.07827721793294626</v>
       </c>
       <c r="T27">
-        <v>0.7417774287557555</v>
+        <v>0.7500512224698909</v>
       </c>
       <c r="U27">
         <v>0.09</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>1.615937336170475</v>
+        <v>1.553785900163918</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07617714127038024</v>
+        <v>0.08917337477194139</v>
       </c>
       <c r="C28">
-        <v>182.7958558851384</v>
+        <v>101.1454576844074</v>
       </c>
       <c r="D28">
-        <v>260.4738558851384</v>
+        <v>182.4264576844074</v>
       </c>
       <c r="E28">
-        <v>-49.32199999999999</v>
+        <v>-45.71899999999999</v>
       </c>
       <c r="F28">
-        <v>93.67800000000001</v>
+        <v>97.28100000000001</v>
       </c>
       <c r="G28">
         <v>16</v>
@@ -3583,45 +3583,45 @@
         <v>13.1</v>
       </c>
       <c r="M28">
-        <v>8.43102</v>
+        <v>14.2808508</v>
       </c>
       <c r="N28">
-        <v>4.668979999999998</v>
+        <v>-1.180850800000004</v>
       </c>
       <c r="O28">
-        <v>1.027175599999999</v>
+        <v>-0.2597871760000008</v>
       </c>
       <c r="P28">
-        <v>3.641804399999998</v>
+        <v>-0.9210636240000027</v>
       </c>
       <c r="Q28">
-        <v>22.0418044</v>
+        <v>17.478936376</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07827721793294626</v>
+        <v>0.07881680080271949</v>
       </c>
       <c r="T28">
-        <v>0.7500512224698909</v>
+        <v>0.7625127206170786</v>
       </c>
       <c r="U28">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V28">
-        <v>0.22</v>
+        <v>0.201808704562616</v>
       </c>
       <c r="W28">
-        <v>0.0702</v>
+        <v>0.117174482170208</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y28">
-        <v>1.553785900163918</v>
+        <v>0.9173122934664366</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08917337477194139</v>
+        <v>0.09018337477194138</v>
       </c>
       <c r="C29">
-        <v>101.1454576844074</v>
+        <v>93.39111220407835</v>
       </c>
       <c r="D29">
-        <v>182.4264576844074</v>
+        <v>178.2751122040784</v>
       </c>
       <c r="E29">
-        <v>-45.71899999999999</v>
+        <v>-42.11599999999999</v>
       </c>
       <c r="F29">
-        <v>97.28100000000001</v>
+        <v>100.884</v>
       </c>
       <c r="G29">
         <v>16</v>
@@ -3665,37 +3665,37 @@
         <v>13.1</v>
       </c>
       <c r="M29">
-        <v>14.2808508</v>
+        <v>14.8097712</v>
       </c>
       <c r="N29">
-        <v>-1.180850800000004</v>
+        <v>-1.709771200000006</v>
       </c>
       <c r="O29">
-        <v>-0.2597871760000008</v>
+        <v>-0.3761496640000013</v>
       </c>
       <c r="P29">
-        <v>-0.9210636240000027</v>
+        <v>-1.333621536000005</v>
       </c>
       <c r="Q29">
-        <v>17.478936376</v>
+        <v>17.06637846399999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07881680080271949</v>
+        <v>0.07927536748053504</v>
       </c>
       <c r="T29">
-        <v>0.7625127206170786</v>
+        <v>0.7731031750700935</v>
       </c>
       <c r="U29">
         <v>0.1468</v>
       </c>
       <c r="V29">
-        <v>0.201808704562616</v>
+        <v>0.1946012508282369</v>
       </c>
       <c r="W29">
-        <v>0.117174482170208</v>
+        <v>0.1182325363784148</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.9173122934664366</v>
+        <v>0.8845511401283495</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09018337477194138</v>
+        <v>0.09119337477194139</v>
       </c>
       <c r="C30">
-        <v>93.39111220407835</v>
+        <v>85.82150112414121</v>
       </c>
       <c r="D30">
-        <v>178.2751122040784</v>
+        <v>174.3085011241412</v>
       </c>
       <c r="E30">
-        <v>-42.11599999999999</v>
+        <v>-38.51299999999998</v>
       </c>
       <c r="F30">
-        <v>100.884</v>
+        <v>104.487</v>
       </c>
       <c r="G30">
         <v>16</v>
@@ -3747,37 +3747,37 @@
         <v>13.1</v>
       </c>
       <c r="M30">
-        <v>14.8097712</v>
+        <v>15.3386916</v>
       </c>
       <c r="N30">
-        <v>-1.709771200000006</v>
+        <v>-2.238691600000006</v>
       </c>
       <c r="O30">
-        <v>-0.3761496640000013</v>
+        <v>-0.4925121520000014</v>
       </c>
       <c r="P30">
-        <v>-1.333621536000005</v>
+        <v>-1.746179448000005</v>
       </c>
       <c r="Q30">
-        <v>17.06637846399999</v>
+        <v>16.65382055199999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07927536748053504</v>
+        <v>0.07974685152955667</v>
       </c>
       <c r="T30">
-        <v>0.7731031750700935</v>
+        <v>0.7839919521837569</v>
       </c>
       <c r="U30">
         <v>0.1468</v>
       </c>
       <c r="V30">
-        <v>0.1946012508282369</v>
+        <v>0.1878908628686425</v>
       </c>
       <c r="W30">
-        <v>0.1182325363784148</v>
+        <v>0.1192176213308833</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.8845511401283495</v>
+        <v>0.8540493766756477</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09119337477194137</v>
+        <v>0.09220337477194138</v>
       </c>
       <c r="C31">
-        <v>85.82150112414135</v>
+        <v>78.42456184708175</v>
       </c>
       <c r="D31">
-        <v>174.3085011241413</v>
+        <v>170.5145618470818</v>
       </c>
       <c r="E31">
-        <v>-38.51300000000001</v>
+        <v>-34.91</v>
       </c>
       <c r="F31">
-        <v>104.487</v>
+        <v>108.09</v>
       </c>
       <c r="G31">
         <v>16</v>
@@ -3829,37 +3829,37 @@
         <v>13.1</v>
       </c>
       <c r="M31">
-        <v>15.3386916</v>
+        <v>15.867612</v>
       </c>
       <c r="N31">
-        <v>-2.238691600000003</v>
+        <v>-2.767612000000003</v>
       </c>
       <c r="O31">
-        <v>-0.4925121520000006</v>
+        <v>-0.6088746400000007</v>
       </c>
       <c r="P31">
-        <v>-1.746179448000002</v>
+        <v>-2.158737360000003</v>
       </c>
       <c r="Q31">
-        <v>16.653820552</v>
+        <v>16.24126264</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.07974685152955666</v>
+        <v>0.08023180655140748</v>
       </c>
       <c r="T31">
-        <v>0.7839919521837568</v>
+        <v>0.7951918372149535</v>
       </c>
       <c r="U31">
         <v>0.1468</v>
       </c>
       <c r="V31">
-        <v>0.1878908628686425</v>
+        <v>0.1816278341063545</v>
       </c>
       <c r="W31">
-        <v>0.1192176213308833</v>
+        <v>0.1201370339531872</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.854049376675648</v>
+        <v>0.825581064119793</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09220337477194138</v>
+        <v>0.1103269040733321</v>
       </c>
       <c r="C32">
-        <v>78.42456184708175</v>
+        <v>26.92951275020634</v>
       </c>
       <c r="D32">
-        <v>170.5145618470818</v>
+        <v>122.6225127502064</v>
       </c>
       <c r="E32">
-        <v>-34.91</v>
+        <v>-31.307</v>
       </c>
       <c r="F32">
-        <v>108.09</v>
+        <v>111.693</v>
       </c>
       <c r="G32">
         <v>16</v>
@@ -3911,45 +3911,45 @@
         <v>13.1</v>
       </c>
       <c r="M32">
-        <v>15.867612</v>
+        <v>22.4279544</v>
       </c>
       <c r="N32">
-        <v>-2.767612000000003</v>
+        <v>-9.327954400000003</v>
       </c>
       <c r="O32">
-        <v>-0.6088746400000007</v>
+        <v>-2.052149968000001</v>
       </c>
       <c r="P32">
-        <v>-2.158737360000003</v>
+        <v>-7.275804432000003</v>
       </c>
       <c r="Q32">
-        <v>16.24126264</v>
+        <v>11.124195568</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08023180655140748</v>
+        <v>0.08127216505416809</v>
       </c>
       <c r="T32">
-        <v>0.7951918372149535</v>
+        <v>0.8192185924750141</v>
       </c>
       <c r="U32">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V32">
-        <v>0.1816278341063545</v>
+        <v>0.1285003504376663</v>
       </c>
       <c r="W32">
-        <v>0.1201370339531872</v>
+        <v>0.1749971296321166</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y32">
-        <v>0.825581064119793</v>
+        <v>0.5840925019893921</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1103269040733321</v>
+        <v>0.1118769040733321</v>
       </c>
       <c r="C33">
-        <v>26.92951275020634</v>
+        <v>20.45009325948858</v>
       </c>
       <c r="D33">
-        <v>122.6225127502064</v>
+        <v>119.7460932594886</v>
       </c>
       <c r="E33">
-        <v>-31.307</v>
+        <v>-27.70399999999999</v>
       </c>
       <c r="F33">
-        <v>111.693</v>
+        <v>115.296</v>
       </c>
       <c r="G33">
         <v>16</v>
@@ -3993,37 +3993,37 @@
         <v>13.1</v>
       </c>
       <c r="M33">
-        <v>22.4279544</v>
+        <v>23.1514368</v>
       </c>
       <c r="N33">
-        <v>-9.327954400000003</v>
+        <v>-10.0514368</v>
       </c>
       <c r="O33">
-        <v>-2.052149968000001</v>
+        <v>-2.211316096000001</v>
       </c>
       <c r="P33">
-        <v>-7.275804432000003</v>
+        <v>-7.840120704000004</v>
       </c>
       <c r="Q33">
-        <v>11.124195568</v>
+        <v>10.55987929599999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08127216505416809</v>
+        <v>0.0817938145402588</v>
       </c>
       <c r="T33">
-        <v>0.8192185924750141</v>
+        <v>0.8312659247172935</v>
       </c>
       <c r="U33">
         <v>0.2008</v>
       </c>
       <c r="V33">
-        <v>0.1285003504376663</v>
+        <v>0.1244847144864892</v>
       </c>
       <c r="W33">
-        <v>0.1749971296321166</v>
+        <v>0.175803469331113</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.5840925019893921</v>
+        <v>0.5658396113022237</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1118769040733321</v>
+        <v>0.1134269040733321</v>
       </c>
       <c r="C34">
-        <v>20.45009325948858</v>
+        <v>14.10252810312794</v>
       </c>
       <c r="D34">
-        <v>119.7460932594886</v>
+        <v>117.001528103128</v>
       </c>
       <c r="E34">
-        <v>-27.70399999999999</v>
+        <v>-24.10099999999998</v>
       </c>
       <c r="F34">
-        <v>115.296</v>
+        <v>118.899</v>
       </c>
       <c r="G34">
         <v>16</v>
@@ -4075,37 +4075,37 @@
         <v>13.1</v>
       </c>
       <c r="M34">
-        <v>23.1514368</v>
+        <v>23.8749192</v>
       </c>
       <c r="N34">
-        <v>-10.0514368</v>
+        <v>-10.77491920000001</v>
       </c>
       <c r="O34">
-        <v>-2.211316096000001</v>
+        <v>-2.370482224000002</v>
       </c>
       <c r="P34">
-        <v>-7.840120704000004</v>
+        <v>-8.404436976000005</v>
       </c>
       <c r="Q34">
-        <v>10.55987929599999</v>
+        <v>9.995563023999994</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.0817938145402588</v>
+        <v>0.08233103565279998</v>
       </c>
       <c r="T34">
-        <v>0.8312659247172935</v>
+        <v>0.8436728788175517</v>
       </c>
       <c r="U34">
         <v>0.2008</v>
       </c>
       <c r="V34">
-        <v>0.1244847144864892</v>
+        <v>0.120712450411141</v>
       </c>
       <c r="W34">
-        <v>0.175803469331113</v>
+        <v>0.1765609399574429</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.5658396113022237</v>
+        <v>0.5486929564142775</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1134269040733321</v>
+        <v>0.1149769040733321</v>
       </c>
       <c r="C35">
-        <v>14.10252810312794</v>
+        <v>7.877954169035718</v>
       </c>
       <c r="D35">
-        <v>117.001528103128</v>
+        <v>114.3799541690357</v>
       </c>
       <c r="E35">
-        <v>-24.10099999999998</v>
+        <v>-20.49799999999999</v>
       </c>
       <c r="F35">
-        <v>118.899</v>
+        <v>122.502</v>
       </c>
       <c r="G35">
         <v>16</v>
@@ -4157,37 +4157,37 @@
         <v>13.1</v>
       </c>
       <c r="M35">
-        <v>23.8749192</v>
+        <v>24.5984016</v>
       </c>
       <c r="N35">
-        <v>-10.77491920000001</v>
+        <v>-11.4984016</v>
       </c>
       <c r="O35">
-        <v>-2.370482224000002</v>
+        <v>-2.529648352000001</v>
       </c>
       <c r="P35">
-        <v>-8.404436976000005</v>
+        <v>-8.968753248000004</v>
       </c>
       <c r="Q35">
-        <v>9.995563023999994</v>
+        <v>9.431246751999995</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08233103565279998</v>
+        <v>0.08288453619299392</v>
       </c>
       <c r="T35">
-        <v>0.8436728788175517</v>
+        <v>0.8564558012238782</v>
       </c>
       <c r="U35">
         <v>0.2008</v>
       </c>
       <c r="V35">
-        <v>0.120712450411141</v>
+        <v>0.1171620842225781</v>
       </c>
       <c r="W35">
-        <v>0.1765609399574429</v>
+        <v>0.1772738534881063</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.5486929564142775</v>
+        <v>0.5325549282844457</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1149769040733321</v>
+        <v>0.1165269040733321</v>
       </c>
       <c r="C36">
-        <v>7.877954169035718</v>
+        <v>1.768285295502267</v>
       </c>
       <c r="D36">
-        <v>114.3799541690357</v>
+        <v>111.8732852955023</v>
       </c>
       <c r="E36">
-        <v>-20.49799999999999</v>
+        <v>-16.89499999999998</v>
       </c>
       <c r="F36">
-        <v>122.502</v>
+        <v>126.105</v>
       </c>
       <c r="G36">
         <v>16</v>
@@ -4239,37 +4239,37 @@
         <v>13.1</v>
       </c>
       <c r="M36">
-        <v>24.5984016</v>
+        <v>25.321884</v>
       </c>
       <c r="N36">
-        <v>-11.4984016</v>
+        <v>-12.22188400000001</v>
       </c>
       <c r="O36">
-        <v>-2.529648352000001</v>
+        <v>-2.688814480000001</v>
       </c>
       <c r="P36">
-        <v>-8.968753248000004</v>
+        <v>-9.533069520000005</v>
       </c>
       <c r="Q36">
-        <v>9.431246751999995</v>
+        <v>8.866930479999994</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08288453619299392</v>
+        <v>0.08345506751903997</v>
       </c>
       <c r="T36">
-        <v>0.8564558012238782</v>
+        <v>0.8696320443196301</v>
       </c>
       <c r="U36">
         <v>0.2008</v>
       </c>
       <c r="V36">
-        <v>0.1171620842225781</v>
+        <v>0.113814596101933</v>
       </c>
       <c r="W36">
-        <v>0.1772738534881063</v>
+        <v>0.1779460291027319</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.5325549282844457</v>
+        <v>0.5173390731906045</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1165269040733321</v>
+        <v>0.1180769040733321</v>
       </c>
       <c r="C37">
-        <v>1.768285295502267</v>
+        <v>-4.233871038478114</v>
       </c>
       <c r="D37">
-        <v>111.8732852955023</v>
+        <v>109.4741289615219</v>
       </c>
       <c r="E37">
-        <v>-16.89499999999998</v>
+        <v>-13.29199999999997</v>
       </c>
       <c r="F37">
-        <v>126.105</v>
+        <v>129.708</v>
       </c>
       <c r="G37">
         <v>16</v>
@@ -4321,37 +4321,37 @@
         <v>13.1</v>
       </c>
       <c r="M37">
-        <v>25.321884</v>
+        <v>26.04536640000001</v>
       </c>
       <c r="N37">
-        <v>-12.22188400000001</v>
+        <v>-12.94536640000001</v>
       </c>
       <c r="O37">
-        <v>-2.688814480000001</v>
+        <v>-2.847980608000002</v>
       </c>
       <c r="P37">
-        <v>-9.533069520000005</v>
+        <v>-10.09738579200001</v>
       </c>
       <c r="Q37">
-        <v>8.866930479999994</v>
+        <v>8.302614207999993</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08345506751903997</v>
+        <v>0.08404342794902497</v>
       </c>
       <c r="T37">
-        <v>0.8696320443196301</v>
+        <v>0.8832200450121244</v>
       </c>
       <c r="U37">
         <v>0.2008</v>
       </c>
       <c r="V37">
-        <v>0.113814596101933</v>
+        <v>0.1106530795435459</v>
       </c>
       <c r="W37">
-        <v>0.1779460291027319</v>
+        <v>0.178580861627656</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.5173390731906045</v>
+        <v>0.5029685433797543</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1180769040733321</v>
+        <v>0.1327276276581769</v>
       </c>
       <c r="C38">
-        <v>-4.233871038478085</v>
+        <v>-26.287566706992</v>
       </c>
       <c r="D38">
-        <v>109.4741289615219</v>
+        <v>91.02343329300801</v>
       </c>
       <c r="E38">
-        <v>-13.292</v>
+        <v>-9.688999999999993</v>
       </c>
       <c r="F38">
-        <v>129.708</v>
+        <v>133.311</v>
       </c>
       <c r="G38">
         <v>16</v>
@@ -4403,45 +4403,45 @@
         <v>13.1</v>
       </c>
       <c r="M38">
-        <v>26.0453664</v>
+        <v>31.4347338</v>
       </c>
       <c r="N38">
-        <v>-12.9453664</v>
+        <v>-18.33473380000001</v>
       </c>
       <c r="O38">
-        <v>-2.847980608</v>
+        <v>-4.033641436000002</v>
       </c>
       <c r="P38">
-        <v>-10.097385792</v>
+        <v>-14.301092364</v>
       </c>
       <c r="Q38">
-        <v>8.302614207999998</v>
+        <v>4.098907635999995</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08404342794902497</v>
+        <v>0.08488971027336631</v>
       </c>
       <c r="T38">
-        <v>0.8832200450121244</v>
+        <v>0.9027646714403308</v>
       </c>
       <c r="U38">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.110653079543546</v>
+        <v>0.09168202340558708</v>
       </c>
       <c r="W38">
-        <v>0.178580861627656</v>
+        <v>0.2141813788809626</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y38">
-        <v>0.5029685433797544</v>
+        <v>0.4167364700253958</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1327276276581769</v>
+        <v>0.1346276276581769</v>
       </c>
       <c r="C39">
-        <v>-26.287566706992</v>
+        <v>-31.83753442206181</v>
       </c>
       <c r="D39">
-        <v>91.02343329300801</v>
+        <v>89.07646557793821</v>
       </c>
       <c r="E39">
-        <v>-9.688999999999993</v>
+        <v>-6.085999999999984</v>
       </c>
       <c r="F39">
-        <v>133.311</v>
+        <v>136.914</v>
       </c>
       <c r="G39">
         <v>16</v>
@@ -4485,37 +4485,37 @@
         <v>13.1</v>
       </c>
       <c r="M39">
-        <v>31.4347338</v>
+        <v>32.28432120000001</v>
       </c>
       <c r="N39">
-        <v>-18.33473380000001</v>
+        <v>-19.18432120000001</v>
       </c>
       <c r="O39">
-        <v>-4.033641436000002</v>
+        <v>-4.220550664000002</v>
       </c>
       <c r="P39">
-        <v>-14.301092364</v>
+        <v>-14.96377053600001</v>
       </c>
       <c r="Q39">
-        <v>4.098907635999995</v>
+        <v>3.43622946399999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08488971027336631</v>
+        <v>0.08552018947132384</v>
       </c>
       <c r="T39">
-        <v>0.9027646714403308</v>
+        <v>0.9173253919474328</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.09168202340558708</v>
+        <v>0.08926933857912425</v>
       </c>
       <c r="W39">
-        <v>0.2141813788809626</v>
+        <v>0.2147502899630425</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.4167364700253958</v>
+        <v>0.4057697208142012</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1346276276581769</v>
+        <v>0.1365276276581769</v>
       </c>
       <c r="C40">
-        <v>-31.83753442206181</v>
+        <v>-37.30595611296864</v>
       </c>
       <c r="D40">
-        <v>89.07646557793821</v>
+        <v>87.21104388703135</v>
       </c>
       <c r="E40">
-        <v>-6.085999999999984</v>
+        <v>-2.483000000000004</v>
       </c>
       <c r="F40">
-        <v>136.914</v>
+        <v>140.517</v>
       </c>
       <c r="G40">
         <v>16</v>
@@ -4567,37 +4567,37 @@
         <v>13.1</v>
       </c>
       <c r="M40">
-        <v>32.28432120000001</v>
+        <v>33.1339086</v>
       </c>
       <c r="N40">
-        <v>-19.18432120000001</v>
+        <v>-20.0339086</v>
       </c>
       <c r="O40">
-        <v>-4.220550664000002</v>
+        <v>-4.407459892</v>
       </c>
       <c r="P40">
-        <v>-14.96377053600001</v>
+        <v>-15.626448708</v>
       </c>
       <c r="Q40">
-        <v>3.43622946399999</v>
+        <v>2.773551291999999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08552018947132384</v>
+        <v>0.08617134011839472</v>
       </c>
       <c r="T40">
-        <v>0.9173253919474328</v>
+        <v>0.932363513126899</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.08926933857912425</v>
+        <v>0.08698038117965955</v>
       </c>
       <c r="W40">
-        <v>0.2147502899630425</v>
+        <v>0.2152900261178363</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.4057697208142012</v>
+        <v>0.3953653689984525</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1365276276581769</v>
+        <v>0.1384276276581769</v>
       </c>
       <c r="C41">
-        <v>-37.30595611296864</v>
+        <v>-42.6978498542274</v>
       </c>
       <c r="D41">
-        <v>87.21104388703135</v>
+        <v>85.4221501457726</v>
       </c>
       <c r="E41">
-        <v>-2.483000000000004</v>
+        <v>1.120000000000005</v>
       </c>
       <c r="F41">
-        <v>140.517</v>
+        <v>144.12</v>
       </c>
       <c r="G41">
         <v>16</v>
@@ -4649,37 +4649,37 @@
         <v>13.1</v>
       </c>
       <c r="M41">
-        <v>33.1339086</v>
+        <v>33.983496</v>
       </c>
       <c r="N41">
-        <v>-20.0339086</v>
+        <v>-20.883496</v>
       </c>
       <c r="O41">
-        <v>-4.407459892</v>
+        <v>-4.594369120000001</v>
       </c>
       <c r="P41">
-        <v>-15.626448708</v>
+        <v>-16.28912688</v>
       </c>
       <c r="Q41">
-        <v>2.773551291999999</v>
+        <v>2.110873119999994</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08617134011839472</v>
+        <v>0.08684419578703463</v>
       </c>
       <c r="T41">
-        <v>0.932363513126899</v>
+        <v>0.9479029050123473</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.08698038117965955</v>
+        <v>0.08480587165016805</v>
       </c>
       <c r="W41">
-        <v>0.2152900261178363</v>
+        <v>0.2158027754648904</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.3953653689984525</v>
+        <v>0.3854812347734912</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1384276276581769</v>
+        <v>0.1403276276581769</v>
       </c>
       <c r="C42">
-        <v>-42.6978498542274</v>
+        <v>-48.01783026829082</v>
       </c>
       <c r="D42">
-        <v>85.4221501457726</v>
+        <v>83.70516973170919</v>
       </c>
       <c r="E42">
-        <v>1.120000000000005</v>
+        <v>4.723000000000013</v>
       </c>
       <c r="F42">
-        <v>144.12</v>
+        <v>147.723</v>
       </c>
       <c r="G42">
         <v>16</v>
@@ -4731,37 +4731,37 @@
         <v>13.1</v>
       </c>
       <c r="M42">
-        <v>33.983496</v>
+        <v>34.83308340000001</v>
       </c>
       <c r="N42">
-        <v>-20.883496</v>
+        <v>-21.73308340000001</v>
       </c>
       <c r="O42">
-        <v>-4.594369120000001</v>
+        <v>-4.781278348000002</v>
       </c>
       <c r="P42">
-        <v>-16.28912688</v>
+        <v>-16.95180505200001</v>
       </c>
       <c r="Q42">
-        <v>2.110873119999994</v>
+        <v>1.44819494799999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08684419578703463</v>
+        <v>0.08753986012240811</v>
       </c>
       <c r="T42">
-        <v>0.9479029050123473</v>
+        <v>0.96396905594476</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.08480587165016805</v>
+        <v>0.0827374357562615</v>
       </c>
       <c r="W42">
-        <v>0.2158027754648904</v>
+        <v>0.2162905126486735</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.3854812347734912</v>
+        <v>0.3760792534375523</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1403276276581769</v>
+        <v>0.1422276276581769</v>
       </c>
       <c r="C43">
-        <v>-48.01783026829082</v>
+        <v>-53.27014827343785</v>
       </c>
       <c r="D43">
-        <v>83.70516973170919</v>
+        <v>82.05585172656217</v>
       </c>
       <c r="E43">
-        <v>4.723000000000013</v>
+        <v>8.326000000000022</v>
       </c>
       <c r="F43">
-        <v>147.723</v>
+        <v>151.326</v>
       </c>
       <c r="G43">
         <v>16</v>
@@ -4813,37 +4813,37 @@
         <v>13.1</v>
       </c>
       <c r="M43">
-        <v>34.83308340000001</v>
+        <v>35.6826708</v>
       </c>
       <c r="N43">
-        <v>-21.73308340000001</v>
+        <v>-22.58267080000001</v>
       </c>
       <c r="O43">
-        <v>-4.781278348000002</v>
+        <v>-4.968187576000001</v>
       </c>
       <c r="P43">
-        <v>-16.95180505200001</v>
+        <v>-17.614483224</v>
       </c>
       <c r="Q43">
-        <v>1.44819494799999</v>
+        <v>0.7855167759999944</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08753986012240811</v>
+        <v>0.08825951288313927</v>
       </c>
       <c r="T43">
-        <v>0.96396905594476</v>
+        <v>0.9805892120817385</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.0827374357562615</v>
+        <v>0.08076749680968386</v>
       </c>
       <c r="W43">
-        <v>0.2162905126486735</v>
+        <v>0.2167550242522766</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.3760792534375523</v>
+        <v>0.367124985498563</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1422276276581769</v>
+        <v>0.1441276276581769</v>
       </c>
       <c r="C44">
-        <v>-53.27014827343783</v>
+        <v>-58.45872622333468</v>
       </c>
       <c r="D44">
-        <v>82.05585172656217</v>
+        <v>80.47027377666532</v>
       </c>
       <c r="E44">
-        <v>8.325999999999993</v>
+        <v>11.929</v>
       </c>
       <c r="F44">
-        <v>151.326</v>
+        <v>154.929</v>
       </c>
       <c r="G44">
         <v>16</v>
@@ -4895,37 +4895,37 @@
         <v>13.1</v>
       </c>
       <c r="M44">
-        <v>35.6826708</v>
+        <v>36.5322582</v>
       </c>
       <c r="N44">
-        <v>-22.5826708</v>
+        <v>-23.4322582</v>
       </c>
       <c r="O44">
-        <v>-4.968187576</v>
+        <v>-5.155096804000001</v>
       </c>
       <c r="P44">
-        <v>-17.614483224</v>
+        <v>-18.277161396</v>
       </c>
       <c r="Q44">
-        <v>0.7855167760000015</v>
+        <v>0.1228386039999947</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08825951288313927</v>
+        <v>0.08900441661793118</v>
       </c>
       <c r="T44">
-        <v>0.9805892120817385</v>
+        <v>0.9977925315919445</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.08076749680968387</v>
+        <v>0.07888918293038889</v>
       </c>
       <c r="W44">
-        <v>0.2167550242522766</v>
+        <v>0.2171979306650143</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.3671249854985631</v>
+        <v>0.3585871951381313</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1441276276581769</v>
+        <v>0.1460276276581769</v>
       </c>
       <c r="C45">
-        <v>-58.45872622333468</v>
+        <v>-63.58718904978311</v>
       </c>
       <c r="D45">
-        <v>80.47027377666532</v>
+        <v>78.9448109502169</v>
       </c>
       <c r="E45">
-        <v>11.929</v>
+        <v>15.53200000000001</v>
       </c>
       <c r="F45">
-        <v>154.929</v>
+        <v>158.532</v>
       </c>
       <c r="G45">
         <v>16</v>
@@ -4977,37 +4977,37 @@
         <v>13.1</v>
       </c>
       <c r="M45">
-        <v>36.5322582</v>
+        <v>37.38184560000001</v>
       </c>
       <c r="N45">
-        <v>-23.4322582</v>
+        <v>-24.28184560000001</v>
       </c>
       <c r="O45">
-        <v>-5.155096804000001</v>
+        <v>-5.342006032000001</v>
       </c>
       <c r="P45">
-        <v>-18.277161396</v>
+        <v>-18.93983956800001</v>
       </c>
       <c r="Q45">
-        <v>0.1228386039999947</v>
+        <v>-0.5398395680000085</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08900441661793118</v>
+        <v>0.08977592405753709</v>
       </c>
       <c r="T45">
-        <v>0.9977925315919445</v>
+        <v>1.015610255370372</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.07888918293038889</v>
+        <v>0.07709624695469822</v>
       </c>
       <c r="W45">
-        <v>0.2171979306650143</v>
+        <v>0.2176207049680822</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3585871951381313</v>
+        <v>0.3504374861577192</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1460276276581769</v>
+        <v>0.1479276276581769</v>
       </c>
       <c r="C46">
-        <v>-63.58718904978311</v>
+        <v>-68.65889192915918</v>
       </c>
       <c r="D46">
-        <v>78.9448109502169</v>
+        <v>77.47610807084084</v>
       </c>
       <c r="E46">
-        <v>15.53200000000001</v>
+        <v>19.13500000000002</v>
       </c>
       <c r="F46">
-        <v>158.532</v>
+        <v>162.135</v>
       </c>
       <c r="G46">
         <v>16</v>
@@ -5059,37 +5059,37 @@
         <v>13.1</v>
       </c>
       <c r="M46">
-        <v>37.38184560000001</v>
+        <v>38.231433</v>
       </c>
       <c r="N46">
-        <v>-24.28184560000001</v>
+        <v>-25.131433</v>
       </c>
       <c r="O46">
-        <v>-5.342006032000001</v>
+        <v>-5.528915260000001</v>
       </c>
       <c r="P46">
-        <v>-18.93983956800001</v>
+        <v>-19.60251774</v>
       </c>
       <c r="Q46">
-        <v>-0.5398395680000085</v>
+        <v>-1.202517740000005</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08977592405753709</v>
+        <v>0.09057548631312869</v>
       </c>
       <c r="T46">
-        <v>1.015610255370372</v>
+        <v>1.034075896377106</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.07709624695469822</v>
+        <v>0.0753829970223716</v>
       </c>
       <c r="W46">
-        <v>0.2176207049680822</v>
+        <v>0.2180246893021248</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3504374861577192</v>
+        <v>0.3426499864653254</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1479276276581769</v>
+        <v>0.1498276276581769</v>
       </c>
       <c r="C47">
-        <v>-68.65889192915918</v>
+        <v>-73.67694491698944</v>
       </c>
       <c r="D47">
-        <v>77.47610807084084</v>
+        <v>76.06105508301056</v>
       </c>
       <c r="E47">
-        <v>19.13500000000002</v>
+        <v>22.738</v>
       </c>
       <c r="F47">
-        <v>162.135</v>
+        <v>165.738</v>
       </c>
       <c r="G47">
         <v>16</v>
@@ -5141,37 +5141,37 @@
         <v>13.1</v>
       </c>
       <c r="M47">
-        <v>38.231433</v>
+        <v>39.0810204</v>
       </c>
       <c r="N47">
-        <v>-25.131433</v>
+        <v>-25.9810204</v>
       </c>
       <c r="O47">
-        <v>-5.528915260000001</v>
+        <v>-5.715824488000001</v>
       </c>
       <c r="P47">
-        <v>-19.60251774</v>
+        <v>-20.265195912</v>
       </c>
       <c r="Q47">
-        <v>-1.202517740000005</v>
+        <v>-1.865195912000004</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09057548631312869</v>
+        <v>0.09140466198559402</v>
       </c>
       <c r="T47">
-        <v>1.034075896377106</v>
+        <v>1.053225450013719</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.0753829970223716</v>
+        <v>0.07374423621753744</v>
       </c>
       <c r="W47">
-        <v>0.2180246893021248</v>
+        <v>0.2184111090999047</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3426499864653254</v>
+        <v>0.3352010737160793</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1498276276581769</v>
+        <v>0.1517276276581769</v>
       </c>
       <c r="C48">
-        <v>-73.67694491698944</v>
+        <v>-78.64423493133837</v>
       </c>
       <c r="D48">
-        <v>76.06105508301056</v>
+        <v>74.69676506866163</v>
       </c>
       <c r="E48">
-        <v>22.738</v>
+        <v>26.34100000000001</v>
       </c>
       <c r="F48">
-        <v>165.738</v>
+        <v>169.341</v>
       </c>
       <c r="G48">
         <v>16</v>
@@ -5223,37 +5223,37 @@
         <v>13.1</v>
       </c>
       <c r="M48">
-        <v>39.0810204</v>
+        <v>39.9306078</v>
       </c>
       <c r="N48">
-        <v>-25.9810204</v>
+        <v>-26.83060780000001</v>
       </c>
       <c r="O48">
-        <v>-5.715824488000001</v>
+        <v>-5.902733716000001</v>
       </c>
       <c r="P48">
-        <v>-20.265195912</v>
+        <v>-20.92787408400001</v>
       </c>
       <c r="Q48">
-        <v>-1.865195912000004</v>
+        <v>-2.527874084000008</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09140466198559402</v>
+        <v>0.09226512730607694</v>
       </c>
       <c r="T48">
-        <v>1.053225450013719</v>
+        <v>1.073097628315865</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.07374423621753744</v>
+        <v>0.07217520991503663</v>
       </c>
       <c r="W48">
-        <v>0.2184111090999047</v>
+        <v>0.2187810855020344</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3352010737160793</v>
+        <v>0.3280691359774393</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1517276276581769</v>
+        <v>0.1536276276581769</v>
       </c>
       <c r="C49">
-        <v>-78.64423493133837</v>
+        <v>-83.56344541201747</v>
       </c>
       <c r="D49">
-        <v>74.69676506866163</v>
+        <v>73.38055458798254</v>
       </c>
       <c r="E49">
-        <v>26.34100000000001</v>
+        <v>29.94400000000002</v>
       </c>
       <c r="F49">
-        <v>169.341</v>
+        <v>172.944</v>
       </c>
       <c r="G49">
         <v>16</v>
@@ -5305,37 +5305,37 @@
         <v>13.1</v>
       </c>
       <c r="M49">
-        <v>39.9306078</v>
+        <v>40.78019520000001</v>
       </c>
       <c r="N49">
-        <v>-26.83060780000001</v>
+        <v>-27.68019520000001</v>
       </c>
       <c r="O49">
-        <v>-5.902733716000001</v>
+        <v>-6.089642944000002</v>
       </c>
       <c r="P49">
-        <v>-20.92787408400001</v>
+        <v>-21.59055225600001</v>
       </c>
       <c r="Q49">
-        <v>-2.527874084000008</v>
+        <v>-3.190552256000011</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09226512730607694</v>
+        <v>0.09315868744657843</v>
       </c>
       <c r="T49">
-        <v>1.073097628315865</v>
+        <v>1.093734121168093</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.07217520991503663</v>
+        <v>0.07067155970847337</v>
       </c>
       <c r="W49">
-        <v>0.2187810855020344</v>
+        <v>0.219135646220742</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3280691359774393</v>
+        <v>0.3212343623112426</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1536276276581769</v>
+        <v>0.155527627658177</v>
       </c>
       <c r="C50">
-        <v>-83.56344541201744</v>
+        <v>-88.43707393732832</v>
       </c>
       <c r="D50">
-        <v>73.38055458798254</v>
+        <v>72.10992606267168</v>
       </c>
       <c r="E50">
-        <v>29.94399999999999</v>
+        <v>33.547</v>
       </c>
       <c r="F50">
-        <v>172.944</v>
+        <v>176.547</v>
       </c>
       <c r="G50">
         <v>16</v>
@@ -5387,37 +5387,37 @@
         <v>13.1</v>
       </c>
       <c r="M50">
-        <v>40.7801952</v>
+        <v>41.6297826</v>
       </c>
       <c r="N50">
-        <v>-27.6801952</v>
+        <v>-28.5297826</v>
       </c>
       <c r="O50">
-        <v>-6.089642944</v>
+        <v>-6.276552172000001</v>
       </c>
       <c r="P50">
-        <v>-21.590552256</v>
+        <v>-22.253230428</v>
       </c>
       <c r="Q50">
-        <v>-3.190552256000004</v>
+        <v>-3.853230428000003</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.0931586874465784</v>
+        <v>0.09408728916121721</v>
       </c>
       <c r="T50">
-        <v>1.093734121168093</v>
+        <v>1.11517988824982</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.07067155970847339</v>
+        <v>0.06922928297972902</v>
       </c>
       <c r="W50">
-        <v>0.219135646220742</v>
+        <v>0.2194757350733799</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3212343623112426</v>
+        <v>0.3146785589987683</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.155527627658177</v>
+        <v>0.1574276276581769</v>
       </c>
       <c r="C51">
-        <v>-88.43707393732832</v>
+        <v>-93.26744804169088</v>
       </c>
       <c r="D51">
-        <v>72.10992606267168</v>
+        <v>70.88255195830912</v>
       </c>
       <c r="E51">
-        <v>33.547</v>
+        <v>37.15000000000001</v>
       </c>
       <c r="F51">
-        <v>176.547</v>
+        <v>180.15</v>
       </c>
       <c r="G51">
         <v>16</v>
@@ -5469,37 +5469,37 @@
         <v>13.1</v>
       </c>
       <c r="M51">
-        <v>41.6297826</v>
+        <v>42.47937</v>
       </c>
       <c r="N51">
-        <v>-28.5297826</v>
+        <v>-29.37937000000001</v>
       </c>
       <c r="O51">
-        <v>-6.276552172000001</v>
+        <v>-6.463461400000001</v>
       </c>
       <c r="P51">
-        <v>-22.253230428</v>
+        <v>-22.91590860000001</v>
       </c>
       <c r="Q51">
-        <v>-3.853230428000003</v>
+        <v>-4.515908600000007</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09408728916121721</v>
+        <v>0.09505303494444156</v>
       </c>
       <c r="T51">
-        <v>1.11517988824982</v>
+        <v>1.137483486014817</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.06922928297972902</v>
+        <v>0.06784469732013444</v>
       </c>
       <c r="W51">
-        <v>0.2194757350733799</v>
+        <v>0.2198022203719123</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3146785589987683</v>
+        <v>0.3083849878187929</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1574276276581769</v>
+        <v>0.1593276276581769</v>
       </c>
       <c r="C52">
-        <v>-93.26744804169088</v>
+        <v>-98.05673944492793</v>
       </c>
       <c r="D52">
-        <v>70.88255195830912</v>
+        <v>69.69626055507209</v>
       </c>
       <c r="E52">
-        <v>37.15000000000001</v>
+        <v>40.75300000000001</v>
       </c>
       <c r="F52">
-        <v>180.15</v>
+        <v>183.753</v>
       </c>
       <c r="G52">
         <v>16</v>
@@ -5551,37 +5551,37 @@
         <v>13.1</v>
       </c>
       <c r="M52">
-        <v>42.47937</v>
+        <v>43.32895740000001</v>
       </c>
       <c r="N52">
-        <v>-29.37937000000001</v>
+        <v>-30.22895740000001</v>
       </c>
       <c r="O52">
-        <v>-6.463461400000001</v>
+        <v>-6.650370628000002</v>
       </c>
       <c r="P52">
-        <v>-22.91590860000001</v>
+        <v>-23.57858677200001</v>
       </c>
       <c r="Q52">
-        <v>-4.515908600000007</v>
+        <v>-5.17858677200001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09505303494444156</v>
+        <v>0.09605819892289955</v>
       </c>
       <c r="T52">
-        <v>1.137483486014817</v>
+        <v>1.160697434708997</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.06784469732013444</v>
+        <v>0.06651440913738671</v>
       </c>
       <c r="W52">
-        <v>0.2198022203719123</v>
+        <v>0.2201159023254042</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3083849878187929</v>
+        <v>0.3023382233517578</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1593276276581769</v>
+        <v>0.1612276276581769</v>
       </c>
       <c r="C53">
-        <v>-98.05673944492793</v>
+        <v>-102.8069768762194</v>
       </c>
       <c r="D53">
-        <v>69.69626055507209</v>
+        <v>68.54902312378061</v>
       </c>
       <c r="E53">
-        <v>40.75300000000001</v>
+        <v>44.35600000000002</v>
       </c>
       <c r="F53">
-        <v>183.753</v>
+        <v>187.356</v>
       </c>
       <c r="G53">
         <v>16</v>
@@ -5633,37 +5633,37 @@
         <v>13.1</v>
       </c>
       <c r="M53">
-        <v>43.32895740000001</v>
+        <v>44.1785448</v>
       </c>
       <c r="N53">
-        <v>-30.22895740000001</v>
+        <v>-31.07854480000001</v>
       </c>
       <c r="O53">
-        <v>-6.650370628000002</v>
+        <v>-6.837279856000001</v>
       </c>
       <c r="P53">
-        <v>-23.57858677200001</v>
+        <v>-24.241264944</v>
       </c>
       <c r="Q53">
-        <v>-5.17858677200001</v>
+        <v>-5.841264944000006</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09605819892289955</v>
+        <v>0.09710524473379328</v>
       </c>
       <c r="T53">
-        <v>1.160697434708997</v>
+        <v>1.184878631265434</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.06651440913738671</v>
+        <v>0.06523528588474466</v>
       </c>
       <c r="W53">
-        <v>0.2201159023254042</v>
+        <v>0.2204175195883772</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3023382233517578</v>
+        <v>0.2965240267488394</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1612276276581769</v>
+        <v>0.163127627658177</v>
       </c>
       <c r="C54">
-        <v>-102.8069768762194</v>
+        <v>-107.5200576520332</v>
       </c>
       <c r="D54">
-        <v>68.54902312378061</v>
+        <v>67.43894234796677</v>
       </c>
       <c r="E54">
-        <v>44.35600000000002</v>
+        <v>47.959</v>
       </c>
       <c r="F54">
-        <v>187.356</v>
+        <v>190.959</v>
       </c>
       <c r="G54">
         <v>16</v>
@@ -5715,37 +5715,37 @@
         <v>13.1</v>
       </c>
       <c r="M54">
-        <v>44.1785448</v>
+        <v>45.0281322</v>
       </c>
       <c r="N54">
-        <v>-31.07854480000001</v>
+        <v>-31.9281322</v>
       </c>
       <c r="O54">
-        <v>-6.837279856000001</v>
+        <v>-7.024189084000001</v>
       </c>
       <c r="P54">
-        <v>-24.241264944</v>
+        <v>-24.903943116</v>
       </c>
       <c r="Q54">
-        <v>-5.841264944000006</v>
+        <v>-6.503943116000006</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09710524473379328</v>
+        <v>0.09819684568557613</v>
       </c>
       <c r="T54">
-        <v>1.184878631265434</v>
+        <v>1.21008881490938</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.06523528588474466</v>
+        <v>0.0640044314340891</v>
       </c>
       <c r="W54">
-        <v>0.2204175195883772</v>
+        <v>0.2207077550678418</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.2965240267488394</v>
+        <v>0.2909292337913141</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.163127627658177</v>
+        <v>0.1650276276581769</v>
       </c>
       <c r="C55">
-        <v>-107.5200576520332</v>
+        <v>-112.1977581470267</v>
       </c>
       <c r="D55">
-        <v>67.43894234796677</v>
+        <v>66.36424185297334</v>
       </c>
       <c r="E55">
-        <v>47.959</v>
+        <v>51.56200000000001</v>
       </c>
       <c r="F55">
-        <v>190.959</v>
+        <v>194.562</v>
       </c>
       <c r="G55">
         <v>16</v>
@@ -5797,37 +5797,37 @@
         <v>13.1</v>
       </c>
       <c r="M55">
-        <v>45.0281322</v>
+        <v>45.87771960000001</v>
       </c>
       <c r="N55">
-        <v>-31.9281322</v>
+        <v>-32.77771960000001</v>
       </c>
       <c r="O55">
-        <v>-7.024189084000001</v>
+        <v>-7.211098312000003</v>
       </c>
       <c r="P55">
-        <v>-24.903943116</v>
+        <v>-25.56662128800001</v>
       </c>
       <c r="Q55">
-        <v>-6.503943116000006</v>
+        <v>-7.166621288000009</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09819684568557613</v>
+        <v>0.09933590754830604</v>
       </c>
       <c r="T55">
-        <v>1.21008881490938</v>
+        <v>1.236395093494366</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.0640044314340891</v>
+        <v>0.06281916418530967</v>
       </c>
       <c r="W55">
-        <v>0.2207077550678418</v>
+        <v>0.220987241085104</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.2909292337913141</v>
+        <v>0.2855416553877711</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1650276276581769</v>
+        <v>0.166927627658177</v>
       </c>
       <c r="C56">
-        <v>-112.1977581470267</v>
+        <v>-116.8417432794729</v>
       </c>
       <c r="D56">
-        <v>66.36424185297334</v>
+        <v>65.32325672052708</v>
       </c>
       <c r="E56">
-        <v>51.56200000000001</v>
+        <v>55.16500000000002</v>
       </c>
       <c r="F56">
-        <v>194.562</v>
+        <v>198.165</v>
       </c>
       <c r="G56">
         <v>16</v>
@@ -5879,37 +5879,37 @@
         <v>13.1</v>
       </c>
       <c r="M56">
-        <v>45.87771960000001</v>
+        <v>46.727307</v>
       </c>
       <c r="N56">
-        <v>-32.77771960000001</v>
+        <v>-33.627307</v>
       </c>
       <c r="O56">
-        <v>-7.211098312000003</v>
+        <v>-7.39800754</v>
       </c>
       <c r="P56">
-        <v>-25.56662128800001</v>
+        <v>-26.22929946</v>
       </c>
       <c r="Q56">
-        <v>-7.166621288000009</v>
+        <v>-7.829299460000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09933590754830604</v>
+        <v>0.1005255943827128</v>
       </c>
       <c r="T56">
-        <v>1.236395093494366</v>
+        <v>1.263870540016463</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.06281916418530967</v>
+        <v>0.06167699756375858</v>
       </c>
       <c r="W56">
-        <v>0.220987241085104</v>
+        <v>0.2212565639744657</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2855416553877711</v>
+        <v>0.2803499889261755</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.166927627658177</v>
+        <v>0.1688276276581769</v>
       </c>
       <c r="C57">
-        <v>-116.8417432794729</v>
+        <v>-121.4535751177479</v>
       </c>
       <c r="D57">
-        <v>65.32325672052708</v>
+        <v>64.31442488225214</v>
       </c>
       <c r="E57">
-        <v>55.16500000000002</v>
+        <v>58.76800000000003</v>
       </c>
       <c r="F57">
-        <v>198.165</v>
+        <v>201.768</v>
       </c>
       <c r="G57">
         <v>16</v>
@@ -5961,37 +5961,37 @@
         <v>13.1</v>
       </c>
       <c r="M57">
-        <v>46.727307</v>
+        <v>47.57689440000001</v>
       </c>
       <c r="N57">
-        <v>-33.627307</v>
+        <v>-34.47689440000001</v>
       </c>
       <c r="O57">
-        <v>-7.39800754</v>
+        <v>-7.584916768000001</v>
       </c>
       <c r="P57">
-        <v>-26.22929946</v>
+        <v>-26.89197763200001</v>
       </c>
       <c r="Q57">
-        <v>-7.829299460000001</v>
+        <v>-8.491977632000008</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1005255943827128</v>
+        <v>0.1017693578914109</v>
       </c>
       <c r="T57">
-        <v>1.263870540016463</v>
+        <v>1.292594870471383</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.06167699756375858</v>
+        <v>0.0605756226072629</v>
       </c>
       <c r="W57">
-        <v>0.2212565639744657</v>
+        <v>0.2215162681892074</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2803499889261755</v>
+        <v>0.2753437391239223</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1688276276581769</v>
+        <v>0.170727627658177</v>
       </c>
       <c r="C58">
-        <v>-121.4535751177479</v>
+        <v>-126.0347207014504</v>
       </c>
       <c r="D58">
-        <v>64.31442488225214</v>
+        <v>63.33627929854963</v>
       </c>
       <c r="E58">
-        <v>58.76800000000003</v>
+        <v>62.37100000000004</v>
       </c>
       <c r="F58">
-        <v>201.768</v>
+        <v>205.371</v>
       </c>
       <c r="G58">
         <v>16</v>
@@ -6043,37 +6043,37 @@
         <v>13.1</v>
       </c>
       <c r="M58">
-        <v>47.57689440000001</v>
+        <v>48.42648180000001</v>
       </c>
       <c r="N58">
-        <v>-34.47689440000001</v>
+        <v>-35.32648180000001</v>
       </c>
       <c r="O58">
-        <v>-7.584916768000001</v>
+        <v>-7.771825996000002</v>
       </c>
       <c r="P58">
-        <v>-26.89197763200001</v>
+        <v>-27.55465580400001</v>
       </c>
       <c r="Q58">
-        <v>-8.491977632000008</v>
+        <v>-9.154655804000008</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1017693578914109</v>
+        <v>0.1030709708656297</v>
       </c>
       <c r="T58">
-        <v>1.292594870471383</v>
+        <v>1.322655216296299</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.0605756226072629</v>
+        <v>0.05951289238608283</v>
       </c>
       <c r="W58">
-        <v>0.2215162681892074</v>
+        <v>0.2217668599753617</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2753437391239223</v>
+        <v>0.2705131472094675</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.170727627658177</v>
+        <v>0.172627627658177</v>
       </c>
       <c r="C59">
-        <v>-126.0347207014504</v>
+        <v>-130.5865591595156</v>
       </c>
       <c r="D59">
-        <v>63.33627929854963</v>
+        <v>62.38744084048449</v>
       </c>
       <c r="E59">
-        <v>62.37100000000004</v>
+        <v>65.97400000000005</v>
       </c>
       <c r="F59">
-        <v>205.371</v>
+        <v>208.974</v>
       </c>
       <c r="G59">
         <v>16</v>
@@ -6125,37 +6125,37 @@
         <v>13.1</v>
       </c>
       <c r="M59">
-        <v>48.42648180000001</v>
+        <v>49.27606920000002</v>
       </c>
       <c r="N59">
-        <v>-35.32648180000001</v>
+        <v>-36.17606920000001</v>
       </c>
       <c r="O59">
-        <v>-7.771825996000002</v>
+        <v>-7.958735224000003</v>
       </c>
       <c r="P59">
-        <v>-27.55465580400001</v>
+        <v>-28.21733397600001</v>
       </c>
       <c r="Q59">
-        <v>-9.154655804000008</v>
+        <v>-9.817333976000015</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1030709708656297</v>
+        <v>0.1044345654100495</v>
       </c>
       <c r="T59">
-        <v>1.322655216296299</v>
+        <v>1.354147007160496</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.05951289238608283</v>
+        <v>0.05848680803459864</v>
       </c>
       <c r="W59">
-        <v>0.2217668599753617</v>
+        <v>0.2220088106654416</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2705131472094675</v>
+        <v>0.2658491274299939</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1726276276581769</v>
+        <v>0.1745276276581769</v>
       </c>
       <c r="C60">
-        <v>-130.5865591595155</v>
+        <v>-135.1103881979538</v>
       </c>
       <c r="D60">
-        <v>62.38744084048449</v>
+        <v>61.46661180204623</v>
       </c>
       <c r="E60">
-        <v>65.97399999999999</v>
+        <v>69.577</v>
       </c>
       <c r="F60">
-        <v>208.974</v>
+        <v>212.577</v>
       </c>
       <c r="G60">
         <v>16</v>
@@ -6207,37 +6207,37 @@
         <v>13.1</v>
       </c>
       <c r="M60">
-        <v>49.2760692</v>
+        <v>50.1256566</v>
       </c>
       <c r="N60">
-        <v>-36.1760692</v>
+        <v>-37.0256566</v>
       </c>
       <c r="O60">
-        <v>-7.958735224</v>
+        <v>-8.145644452000001</v>
       </c>
       <c r="P60">
-        <v>-28.217333976</v>
+        <v>-28.88001214800001</v>
       </c>
       <c r="Q60">
-        <v>-9.817333976</v>
+        <v>-10.48001214800001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1044345654100494</v>
+        <v>0.1058646767615141</v>
       </c>
       <c r="T60">
-        <v>1.354147007160496</v>
+        <v>1.387174982944898</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.05848680803459866</v>
+        <v>0.05749550620350376</v>
       </c>
       <c r="W60">
-        <v>0.2220088106654416</v>
+        <v>0.2222425596372138</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.265849127429994</v>
+        <v>0.2613432100159262</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1745276276581769</v>
+        <v>0.1764276276581769</v>
       </c>
       <c r="C61">
-        <v>-135.1103881979538</v>
+        <v>-139.6074300213994</v>
       </c>
       <c r="D61">
-        <v>61.46661180204623</v>
+        <v>60.57256997860063</v>
       </c>
       <c r="E61">
-        <v>69.577</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="F61">
-        <v>212.577</v>
+        <v>216.18</v>
       </c>
       <c r="G61">
         <v>16</v>
@@ -6289,37 +6289,37 @@
         <v>13.1</v>
       </c>
       <c r="M61">
-        <v>50.1256566</v>
+        <v>50.975244</v>
       </c>
       <c r="N61">
-        <v>-37.0256566</v>
+        <v>-37.87524400000001</v>
       </c>
       <c r="O61">
-        <v>-8.145644452000001</v>
+        <v>-8.332553680000002</v>
       </c>
       <c r="P61">
-        <v>-28.88001214800001</v>
+        <v>-29.54269032000001</v>
       </c>
       <c r="Q61">
-        <v>-10.48001214800001</v>
+        <v>-11.14269032000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1058646767615141</v>
+        <v>0.1073662936805519</v>
       </c>
       <c r="T61">
-        <v>1.387174982944898</v>
+        <v>1.421854357518521</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.05749550620350376</v>
+        <v>0.0565372477667787</v>
       </c>
       <c r="W61">
-        <v>0.2222425596372138</v>
+        <v>0.2224685169765936</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2613432100159262</v>
+        <v>0.256987489848994</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1764276276581769</v>
+        <v>0.1783276276581769</v>
       </c>
       <c r="C62">
-        <v>-139.6074300213994</v>
+        <v>-144.0788367452878</v>
       </c>
       <c r="D62">
-        <v>60.57256997860063</v>
+        <v>59.7041632547122</v>
       </c>
       <c r="E62">
-        <v>73.18000000000001</v>
+        <v>76.78300000000002</v>
       </c>
       <c r="F62">
-        <v>216.18</v>
+        <v>219.783</v>
       </c>
       <c r="G62">
         <v>16</v>
@@ -6371,37 +6371,37 @@
         <v>13.1</v>
       </c>
       <c r="M62">
-        <v>50.975244</v>
+        <v>51.82483140000001</v>
       </c>
       <c r="N62">
-        <v>-37.87524400000001</v>
+        <v>-38.72483140000001</v>
       </c>
       <c r="O62">
-        <v>-8.332553680000002</v>
+        <v>-8.519462908000003</v>
       </c>
       <c r="P62">
-        <v>-29.54269032000001</v>
+        <v>-30.20536849200001</v>
       </c>
       <c r="Q62">
-        <v>-11.14269032000001</v>
+        <v>-11.80536849200001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1073662936805519</v>
+        <v>0.1089449165954379</v>
       </c>
       <c r="T62">
-        <v>1.421854357518521</v>
+        <v>1.458312161557457</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.0565372477667787</v>
+        <v>0.05561040763945445</v>
       </c>
       <c r="W62">
-        <v>0.2224685169765936</v>
+        <v>0.2226870658786166</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.256987489848994</v>
+        <v>0.2527745801793384</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1783276276581769</v>
+        <v>0.1802276276581769</v>
       </c>
       <c r="C63">
-        <v>-144.0788367452878</v>
+        <v>-148.5256953490593</v>
       </c>
       <c r="D63">
-        <v>59.7041632547122</v>
+        <v>58.86030465094065</v>
       </c>
       <c r="E63">
-        <v>76.78300000000002</v>
+        <v>80.386</v>
       </c>
       <c r="F63">
-        <v>219.783</v>
+        <v>223.386</v>
       </c>
       <c r="G63">
         <v>16</v>
@@ -6453,37 +6453,37 @@
         <v>13.1</v>
       </c>
       <c r="M63">
-        <v>51.82483140000001</v>
+        <v>52.6744188</v>
       </c>
       <c r="N63">
-        <v>-38.72483140000001</v>
+        <v>-39.5744188</v>
       </c>
       <c r="O63">
-        <v>-8.519462908000003</v>
+        <v>-8.706372136000001</v>
       </c>
       <c r="P63">
-        <v>-30.20536849200001</v>
+        <v>-30.868046664</v>
       </c>
       <c r="Q63">
-        <v>-11.80536849200001</v>
+        <v>-12.46804666400001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1089449165954379</v>
+        <v>0.1106066249268968</v>
       </c>
       <c r="T63">
-        <v>1.458312161557457</v>
+        <v>1.496688797387917</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.05561040763945445</v>
+        <v>0.05471346558075359</v>
       </c>
       <c r="W63">
-        <v>0.2226870658786166</v>
+        <v>0.2228985648160583</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2527745801793384</v>
+        <v>0.2486975708216072</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1802276276581769</v>
+        <v>0.1821276276581769</v>
       </c>
       <c r="C64">
-        <v>-148.5256953490593</v>
+        <v>-152.9490322151655</v>
       </c>
       <c r="D64">
-        <v>58.86030465094065</v>
+        <v>58.03996778483454</v>
       </c>
       <c r="E64">
-        <v>80.386</v>
+        <v>83.989</v>
       </c>
       <c r="F64">
-        <v>223.386</v>
+        <v>226.989</v>
       </c>
       <c r="G64">
         <v>16</v>
@@ -6535,37 +6535,37 @@
         <v>13.1</v>
       </c>
       <c r="M64">
-        <v>52.6744188</v>
+        <v>53.5240062</v>
       </c>
       <c r="N64">
-        <v>-39.5744188</v>
+        <v>-40.42400620000001</v>
       </c>
       <c r="O64">
-        <v>-8.706372136000001</v>
+        <v>-8.893281364000002</v>
       </c>
       <c r="P64">
-        <v>-30.868046664</v>
+        <v>-31.530724836</v>
       </c>
       <c r="Q64">
-        <v>-12.46804666400001</v>
+        <v>-13.13072483600001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1106066249268968</v>
+        <v>0.1123581553303264</v>
       </c>
       <c r="T64">
-        <v>1.496688797387917</v>
+        <v>1.537139845965968</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.05471346558075359</v>
+        <v>0.05384499787312257</v>
       </c>
       <c r="W64">
-        <v>0.2228985648160583</v>
+        <v>0.2231033495015177</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2486975708216072</v>
+        <v>0.2447499903323752</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1821276276581769</v>
+        <v>0.1840276276581769</v>
       </c>
       <c r="C65">
-        <v>-152.9490322151655</v>
+        <v>-157.3498172937309</v>
       </c>
       <c r="D65">
-        <v>58.03996778483454</v>
+        <v>57.24218270626915</v>
       </c>
       <c r="E65">
-        <v>83.989</v>
+        <v>87.59200000000001</v>
       </c>
       <c r="F65">
-        <v>226.989</v>
+        <v>230.592</v>
       </c>
       <c r="G65">
         <v>16</v>
@@ -6617,37 +6617,37 @@
         <v>13.1</v>
       </c>
       <c r="M65">
-        <v>53.5240062</v>
+        <v>54.37359360000001</v>
       </c>
       <c r="N65">
-        <v>-40.42400620000001</v>
+        <v>-41.27359360000001</v>
       </c>
       <c r="O65">
-        <v>-8.893281364000002</v>
+        <v>-9.080190592000003</v>
       </c>
       <c r="P65">
-        <v>-31.530724836</v>
+        <v>-32.19340300800001</v>
       </c>
       <c r="Q65">
-        <v>-13.13072483600001</v>
+        <v>-13.79340300800001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1123581553303264</v>
+        <v>0.1142069929783911</v>
       </c>
       <c r="T65">
-        <v>1.537139845965968</v>
+        <v>1.579838175020579</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.05384499787312257</v>
+        <v>0.05300366978135503</v>
       </c>
       <c r="W65">
-        <v>0.2231033495015177</v>
+        <v>0.2233017346655565</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2447499903323752</v>
+        <v>0.2409257717334319</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1840276276581769</v>
+        <v>0.1859276276581769</v>
       </c>
       <c r="C66">
-        <v>-157.3498172937309</v>
+        <v>-161.7289679284024</v>
       </c>
       <c r="D66">
-        <v>57.24218270626915</v>
+        <v>56.46603207159761</v>
       </c>
       <c r="E66">
-        <v>87.59200000000001</v>
+        <v>91.19500000000002</v>
       </c>
       <c r="F66">
-        <v>230.592</v>
+        <v>234.195</v>
       </c>
       <c r="G66">
         <v>16</v>
@@ -6699,37 +6699,37 @@
         <v>13.1</v>
       </c>
       <c r="M66">
-        <v>54.37359360000001</v>
+        <v>55.223181</v>
       </c>
       <c r="N66">
-        <v>-41.27359360000001</v>
+        <v>-42.123181</v>
       </c>
       <c r="O66">
-        <v>-9.080190592000003</v>
+        <v>-9.26709982</v>
       </c>
       <c r="P66">
-        <v>-32.19340300800001</v>
+        <v>-32.85608118</v>
       </c>
       <c r="Q66">
-        <v>-13.79340300800001</v>
+        <v>-14.45608118000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1142069929783911</v>
+        <v>0.1161614784920594</v>
       </c>
       <c r="T66">
-        <v>1.579838175020579</v>
+        <v>1.624976408592596</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.05300366978135503</v>
+        <v>0.05218822870779573</v>
       </c>
       <c r="W66">
-        <v>0.2233017346655565</v>
+        <v>0.2234940156707018</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2409257717334319</v>
+        <v>0.2372192213990715</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1859276276581769</v>
+        <v>0.1878276276581769</v>
       </c>
       <c r="C67">
-        <v>-161.7289679284024</v>
+        <v>-166.0873523751119</v>
       </c>
       <c r="D67">
-        <v>56.46603207159761</v>
+        <v>55.71064762488811</v>
       </c>
       <c r="E67">
-        <v>91.19500000000002</v>
+        <v>94.79800000000003</v>
       </c>
       <c r="F67">
-        <v>234.195</v>
+        <v>237.798</v>
       </c>
       <c r="G67">
         <v>16</v>
@@ -6781,37 +6781,37 @@
         <v>13.1</v>
       </c>
       <c r="M67">
-        <v>55.223181</v>
+        <v>56.07276840000001</v>
       </c>
       <c r="N67">
-        <v>-42.123181</v>
+        <v>-42.97276840000001</v>
       </c>
       <c r="O67">
-        <v>-9.26709982</v>
+        <v>-9.454009048000001</v>
       </c>
       <c r="P67">
-        <v>-32.85608118</v>
+        <v>-33.518759352</v>
       </c>
       <c r="Q67">
-        <v>-14.45608118000001</v>
+        <v>-15.118759352</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1161614784920594</v>
+        <v>0.1182309337418258</v>
       </c>
       <c r="T67">
-        <v>1.624976408592596</v>
+        <v>1.67276983237473</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.05218822870779573</v>
+        <v>0.05139749796979881</v>
       </c>
       <c r="W67">
-        <v>0.2234940156707018</v>
+        <v>0.2236804699787214</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2372192213990715</v>
+        <v>0.2336249907718129</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1878276276581769</v>
+        <v>0.1897276276581769</v>
       </c>
       <c r="C68">
-        <v>-166.0873523751119</v>
+        <v>-170.4257930421302</v>
       </c>
       <c r="D68">
-        <v>55.71064762488811</v>
+        <v>54.97520695786984</v>
       </c>
       <c r="E68">
-        <v>94.79800000000003</v>
+        <v>98.40100000000001</v>
       </c>
       <c r="F68">
-        <v>237.798</v>
+        <v>241.401</v>
       </c>
       <c r="G68">
         <v>16</v>
@@ -6863,37 +6863,37 @@
         <v>13.1</v>
       </c>
       <c r="M68">
-        <v>56.07276840000001</v>
+        <v>56.92235580000001</v>
       </c>
       <c r="N68">
-        <v>-42.97276840000001</v>
+        <v>-43.82235580000001</v>
       </c>
       <c r="O68">
-        <v>-9.454009048000001</v>
+        <v>-9.640918276000003</v>
       </c>
       <c r="P68">
-        <v>-33.518759352</v>
+        <v>-34.18143752400001</v>
       </c>
       <c r="Q68">
-        <v>-15.118759352</v>
+        <v>-15.78143752400001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1182309337418258</v>
+        <v>0.1204258105218811</v>
       </c>
       <c r="T68">
-        <v>1.67276983237473</v>
+        <v>1.723459827295177</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.05139749796979881</v>
+        <v>0.05063037113442868</v>
       </c>
       <c r="W68">
-        <v>0.2236804699787214</v>
+        <v>0.2238613584865017</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2336249907718129</v>
+        <v>0.2301380506110394</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1897276276581769</v>
+        <v>0.191627627658177</v>
       </c>
       <c r="C69">
-        <v>-170.4257930421302</v>
+        <v>-174.7450694768315</v>
       </c>
       <c r="D69">
-        <v>54.97520695786984</v>
+        <v>54.2589305231685</v>
       </c>
       <c r="E69">
-        <v>98.40100000000001</v>
+        <v>102.004</v>
       </c>
       <c r="F69">
-        <v>241.401</v>
+        <v>245.004</v>
       </c>
       <c r="G69">
         <v>16</v>
@@ -6945,37 +6945,37 @@
         <v>13.1</v>
       </c>
       <c r="M69">
-        <v>56.92235580000001</v>
+        <v>57.77194320000001</v>
       </c>
       <c r="N69">
-        <v>-43.82235580000001</v>
+        <v>-44.67194320000002</v>
       </c>
       <c r="O69">
-        <v>-9.640918276000003</v>
+        <v>-9.827827504000004</v>
       </c>
       <c r="P69">
-        <v>-34.18143752400001</v>
+        <v>-34.84411569600001</v>
       </c>
       <c r="Q69">
-        <v>-15.78143752400001</v>
+        <v>-16.44411569600001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1204258105218811</v>
+        <v>0.1227578671006899</v>
       </c>
       <c r="T69">
-        <v>1.723459827295177</v>
+        <v>1.777317946898151</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.05063037113442868</v>
+        <v>0.04988580685304003</v>
       </c>
       <c r="W69">
-        <v>0.2238613584865017</v>
+        <v>0.2240369267440532</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2301380506110394</v>
+        <v>0.2267536675138182</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.191627627658177</v>
+        <v>0.1935276276581769</v>
       </c>
       <c r="C70">
-        <v>-174.7450694768315</v>
+        <v>-179.0459211219724</v>
       </c>
       <c r="D70">
-        <v>54.2589305231685</v>
+        <v>53.56107887802763</v>
       </c>
       <c r="E70">
-        <v>102.004</v>
+        <v>105.607</v>
       </c>
       <c r="F70">
-        <v>245.004</v>
+        <v>248.607</v>
       </c>
       <c r="G70">
         <v>16</v>
@@ -7027,37 +7027,37 @@
         <v>13.1</v>
       </c>
       <c r="M70">
-        <v>57.77194320000001</v>
+        <v>58.62153060000001</v>
       </c>
       <c r="N70">
-        <v>-44.67194320000002</v>
+        <v>-45.52153060000001</v>
       </c>
       <c r="O70">
-        <v>-9.827827504000004</v>
+        <v>-10.014736732</v>
       </c>
       <c r="P70">
-        <v>-34.84411569600001</v>
+        <v>-35.506793868</v>
       </c>
       <c r="Q70">
-        <v>-16.44411569600001</v>
+        <v>-17.106793868</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1227578671006899</v>
+        <v>0.1252403789426477</v>
       </c>
       <c r="T70">
-        <v>1.777317946898151</v>
+        <v>1.834650783894866</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.04988580685304003</v>
+        <v>0.04916282414502495</v>
       </c>
       <c r="W70">
-        <v>0.2240369267440532</v>
+        <v>0.2242074060666031</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2267536675138182</v>
+        <v>0.2234673824773862</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1935276276581769</v>
+        <v>0.195427627658177</v>
       </c>
       <c r="C71">
-        <v>-179.0459211219724</v>
+        <v>-183.3290498619718</v>
       </c>
       <c r="D71">
-        <v>53.56107887802763</v>
+        <v>52.88095013802818</v>
       </c>
       <c r="E71">
-        <v>105.607</v>
+        <v>109.21</v>
       </c>
       <c r="F71">
-        <v>248.607</v>
+        <v>252.21</v>
       </c>
       <c r="G71">
         <v>16</v>
@@ -7109,37 +7109,37 @@
         <v>13.1</v>
       </c>
       <c r="M71">
-        <v>58.62153060000001</v>
+        <v>59.47111800000001</v>
       </c>
       <c r="N71">
-        <v>-45.52153060000001</v>
+        <v>-46.37111800000001</v>
       </c>
       <c r="O71">
-        <v>-10.014736732</v>
+        <v>-10.20164596</v>
       </c>
       <c r="P71">
-        <v>-35.506793868</v>
+        <v>-36.16947204000001</v>
       </c>
       <c r="Q71">
-        <v>-17.106793868</v>
+        <v>-17.76947204000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1252403789426477</v>
+        <v>0.1278883915740693</v>
       </c>
       <c r="T71">
-        <v>1.834650783894866</v>
+        <v>1.895805810024695</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.04916282414502495</v>
+        <v>0.04846049808581031</v>
       </c>
       <c r="W71">
-        <v>0.2242074060666031</v>
+        <v>0.2243730145513659</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2234673824773862</v>
+        <v>0.2202749912991379</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.195427627658177</v>
+        <v>0.1973276276581769</v>
       </c>
       <c r="C72">
-        <v>-183.3290498619718</v>
+        <v>-187.5951223776249</v>
       </c>
       <c r="D72">
-        <v>52.88095013802818</v>
+        <v>52.21787762237516</v>
       </c>
       <c r="E72">
-        <v>109.21</v>
+        <v>112.813</v>
       </c>
       <c r="F72">
-        <v>252.21</v>
+        <v>255.813</v>
       </c>
       <c r="G72">
         <v>16</v>
@@ -7191,37 +7191,37 @@
         <v>13.1</v>
       </c>
       <c r="M72">
-        <v>59.47111800000001</v>
+        <v>60.32070540000002</v>
       </c>
       <c r="N72">
-        <v>-46.37111800000001</v>
+        <v>-47.22070540000001</v>
       </c>
       <c r="O72">
-        <v>-10.20164596</v>
+        <v>-10.388555188</v>
       </c>
       <c r="P72">
-        <v>-36.16947204000001</v>
+        <v>-36.83215021200001</v>
       </c>
       <c r="Q72">
-        <v>-17.76947204000001</v>
+        <v>-18.43215021200001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1278883915740693</v>
+        <v>0.1307190257662786</v>
       </c>
       <c r="T72">
-        <v>1.895805810024695</v>
+        <v>1.961178424163478</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.04846049808581031</v>
+        <v>0.0477779558592496</v>
       </c>
       <c r="W72">
-        <v>0.2243730145513659</v>
+        <v>0.224533958008389</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2202749912991379</v>
+        <v>0.2171725266329527</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1973276276581769</v>
+        <v>0.1992276276581769</v>
       </c>
       <c r="C73">
-        <v>-187.5951223776249</v>
+        <v>-191.8447723258568</v>
       </c>
       <c r="D73">
-        <v>52.21787762237512</v>
+        <v>51.57122767414318</v>
       </c>
       <c r="E73">
-        <v>112.813</v>
+        <v>116.416</v>
       </c>
       <c r="F73">
-        <v>255.813</v>
+        <v>259.416</v>
       </c>
       <c r="G73">
         <v>16</v>
@@ -7273,37 +7273,37 @@
         <v>13.1</v>
       </c>
       <c r="M73">
-        <v>60.3207054</v>
+        <v>61.1702928</v>
       </c>
       <c r="N73">
-        <v>-47.2207054</v>
+        <v>-48.0702928</v>
       </c>
       <c r="O73">
-        <v>-10.388555188</v>
+        <v>-10.575464416</v>
       </c>
       <c r="P73">
-        <v>-36.832150212</v>
+        <v>-37.494828384</v>
       </c>
       <c r="Q73">
-        <v>-18.432150212</v>
+        <v>-19.094828384</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1307190257662785</v>
+        <v>0.1337518481150742</v>
       </c>
       <c r="T73">
-        <v>1.961178424163477</v>
+        <v>2.031220510740744</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.04777795585924961</v>
+        <v>0.04711437313898226</v>
       </c>
       <c r="W73">
-        <v>0.224533958008389</v>
+        <v>0.224690430813828</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2171725266329528</v>
+        <v>0.2141562415408284</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1992276276581769</v>
+        <v>0.2011276276581769</v>
       </c>
       <c r="C74">
-        <v>-191.8447723258568</v>
+        <v>-196.0786023594972</v>
       </c>
       <c r="D74">
-        <v>51.57122767414318</v>
+        <v>50.94039764050286</v>
       </c>
       <c r="E74">
-        <v>116.416</v>
+        <v>120.019</v>
       </c>
       <c r="F74">
-        <v>259.416</v>
+        <v>263.019</v>
       </c>
       <c r="G74">
         <v>16</v>
@@ -7355,37 +7355,37 @@
         <v>13.1</v>
       </c>
       <c r="M74">
-        <v>61.1702928</v>
+        <v>62.0198802</v>
       </c>
       <c r="N74">
-        <v>-48.0702928</v>
+        <v>-48.91988020000001</v>
       </c>
       <c r="O74">
-        <v>-10.575464416</v>
+        <v>-10.762373644</v>
       </c>
       <c r="P74">
-        <v>-37.494828384</v>
+        <v>-38.15750655600001</v>
       </c>
       <c r="Q74">
-        <v>-19.094828384</v>
+        <v>-19.75750655600001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1337518481150742</v>
+        <v>0.1370093239711881</v>
       </c>
       <c r="T74">
-        <v>2.031220510740744</v>
+        <v>2.106450900027438</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.04711437313898226</v>
+        <v>0.04646897076721537</v>
       </c>
       <c r="W74">
-        <v>0.224690430813828</v>
+        <v>0.2248426166930906</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2141562415408284</v>
+        <v>0.2112225943964334</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2011276276581769</v>
+        <v>0.2030276276581769</v>
       </c>
       <c r="C75">
-        <v>-196.0786023594972</v>
+        <v>-200.2971860006074</v>
       </c>
       <c r="D75">
-        <v>50.94039764050286</v>
+        <v>50.32481399939262</v>
       </c>
       <c r="E75">
-        <v>120.019</v>
+        <v>123.622</v>
       </c>
       <c r="F75">
-        <v>263.019</v>
+        <v>266.622</v>
       </c>
       <c r="G75">
         <v>16</v>
@@ -7437,37 +7437,37 @@
         <v>13.1</v>
       </c>
       <c r="M75">
-        <v>62.0198802</v>
+        <v>62.86946760000001</v>
       </c>
       <c r="N75">
-        <v>-48.91988020000001</v>
+        <v>-49.76946760000001</v>
       </c>
       <c r="O75">
-        <v>-10.762373644</v>
+        <v>-10.949282872</v>
       </c>
       <c r="P75">
-        <v>-38.15750655600001</v>
+        <v>-38.82018472800001</v>
       </c>
       <c r="Q75">
-        <v>-19.75750655600001</v>
+        <v>-20.42018472800001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1370093239711881</v>
+        <v>0.1405173748931568</v>
       </c>
       <c r="T75">
-        <v>2.106450900027438</v>
+        <v>2.187468242336186</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.04646897076721537</v>
+        <v>0.04584101170279354</v>
       </c>
       <c r="W75">
-        <v>0.2248426166930906</v>
+        <v>0.2249906894404813</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2112225943964334</v>
+        <v>0.2083682350126979</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2030276276581769</v>
+        <v>0.204927627658177</v>
       </c>
       <c r="C76">
-        <v>-200.2971860006074</v>
+        <v>-204.5010693796034</v>
       </c>
       <c r="D76">
-        <v>50.32481399939262</v>
+        <v>49.72393062039665</v>
       </c>
       <c r="E76">
-        <v>123.622</v>
+        <v>127.225</v>
       </c>
       <c r="F76">
-        <v>266.622</v>
+        <v>270.225</v>
       </c>
       <c r="G76">
         <v>16</v>
@@ -7519,37 +7519,37 @@
         <v>13.1</v>
       </c>
       <c r="M76">
-        <v>62.86946760000001</v>
+        <v>63.719055</v>
       </c>
       <c r="N76">
-        <v>-49.76946760000001</v>
+        <v>-50.619055</v>
       </c>
       <c r="O76">
-        <v>-10.949282872</v>
+        <v>-11.1361921</v>
       </c>
       <c r="P76">
-        <v>-38.82018472800001</v>
+        <v>-39.4828629</v>
       </c>
       <c r="Q76">
-        <v>-20.42018472800001</v>
+        <v>-21.0828629</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1405173748931568</v>
+        <v>0.1443060698888831</v>
       </c>
       <c r="T76">
-        <v>2.187468242336186</v>
+        <v>2.274966972029633</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.04584101170279354</v>
+        <v>0.04522979821342296</v>
       </c>
       <c r="W76">
-        <v>0.2249906894404813</v>
+        <v>0.2251348135812749</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2083682350126979</v>
+        <v>0.2055899918791954</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.204927627658177</v>
+        <v>0.2068276276581769</v>
       </c>
       <c r="C77">
-        <v>-204.5010693796034</v>
+        <v>-208.6907728512542</v>
       </c>
       <c r="D77">
-        <v>49.72393062039665</v>
+        <v>49.13722714874587</v>
       </c>
       <c r="E77">
-        <v>127.225</v>
+        <v>130.828</v>
       </c>
       <c r="F77">
-        <v>270.225</v>
+        <v>273.828</v>
       </c>
       <c r="G77">
         <v>16</v>
@@ -7601,37 +7601,37 @@
         <v>13.1</v>
       </c>
       <c r="M77">
-        <v>63.719055</v>
+        <v>64.56864240000002</v>
       </c>
       <c r="N77">
-        <v>-50.619055</v>
+        <v>-51.46864240000002</v>
       </c>
       <c r="O77">
-        <v>-11.1361921</v>
+        <v>-11.32310132800001</v>
       </c>
       <c r="P77">
-        <v>-39.4828629</v>
+        <v>-40.14554107200001</v>
       </c>
       <c r="Q77">
-        <v>-21.0828629</v>
+        <v>-21.74554107200002</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1443060698888831</v>
+        <v>0.1484104894675866</v>
       </c>
       <c r="T77">
-        <v>2.274966972029633</v>
+        <v>2.369757262530868</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.04522979821342296</v>
+        <v>0.04463466928956213</v>
       </c>
       <c r="W77">
-        <v>0.2251348135812749</v>
+        <v>0.2252751449815213</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2055899918791954</v>
+        <v>0.2028848604071005</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2068276276581769</v>
+        <v>0.2087276276581769</v>
       </c>
       <c r="C78">
-        <v>-208.6907728512542</v>
+        <v>-212.8667924976121</v>
       </c>
       <c r="D78">
-        <v>49.13722714874587</v>
+        <v>48.56420750238795</v>
       </c>
       <c r="E78">
-        <v>130.828</v>
+        <v>134.431</v>
       </c>
       <c r="F78">
-        <v>273.828</v>
+        <v>277.431</v>
       </c>
       <c r="G78">
         <v>16</v>
@@ -7683,37 +7683,37 @@
         <v>13.1</v>
       </c>
       <c r="M78">
-        <v>64.56864240000002</v>
+        <v>65.41822980000001</v>
       </c>
       <c r="N78">
-        <v>-51.46864240000002</v>
+        <v>-52.31822980000001</v>
       </c>
       <c r="O78">
-        <v>-11.32310132800001</v>
+        <v>-11.510010556</v>
       </c>
       <c r="P78">
-        <v>-40.14554107200001</v>
+        <v>-40.80821924400001</v>
       </c>
       <c r="Q78">
-        <v>-21.74554107200002</v>
+        <v>-22.40821924400001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1484104894675866</v>
+        <v>0.1528718150966121</v>
       </c>
       <c r="T78">
-        <v>2.369757262530868</v>
+        <v>2.472790186988732</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.04463466928956213</v>
+        <v>0.04405499825982755</v>
       </c>
       <c r="W78">
-        <v>0.2252751449815213</v>
+        <v>0.2254118314103327</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2028848604071005</v>
+        <v>0.2002499920901252</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2087276276581769</v>
+        <v>0.2106276276581769</v>
       </c>
       <c r="C79">
-        <v>-212.8667924976121</v>
+        <v>-217.0296015269933</v>
       </c>
       <c r="D79">
-        <v>48.56420750238795</v>
+        <v>48.00439847300667</v>
       </c>
       <c r="E79">
-        <v>134.431</v>
+        <v>138.034</v>
       </c>
       <c r="F79">
-        <v>277.431</v>
+        <v>281.034</v>
       </c>
       <c r="G79">
         <v>16</v>
@@ -7765,37 +7765,37 @@
         <v>13.1</v>
       </c>
       <c r="M79">
-        <v>65.41822980000001</v>
+        <v>66.2678172</v>
       </c>
       <c r="N79">
-        <v>-52.31822980000001</v>
+        <v>-53.1678172</v>
       </c>
       <c r="O79">
-        <v>-11.510010556</v>
+        <v>-11.696919784</v>
       </c>
       <c r="P79">
-        <v>-40.80821924400001</v>
+        <v>-41.470897416</v>
       </c>
       <c r="Q79">
-        <v>-22.40821924400001</v>
+        <v>-23.070897416</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1528718150966121</v>
+        <v>0.1577387157828217</v>
       </c>
       <c r="T79">
-        <v>2.472790186988732</v>
+        <v>2.585189740942766</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.04405499825982755</v>
+        <v>0.04349019058982977</v>
       </c>
       <c r="W79">
-        <v>0.2254118314103327</v>
+        <v>0.2255450130589182</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2002499920901252</v>
+        <v>0.1976826844992262</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2106276276581769</v>
+        <v>0.212527627658177</v>
       </c>
       <c r="C80">
-        <v>-217.0296015269933</v>
+        <v>-221.1796515773048</v>
       </c>
       <c r="D80">
-        <v>48.00439847300667</v>
+        <v>47.45734842269525</v>
       </c>
       <c r="E80">
-        <v>138.034</v>
+        <v>141.637</v>
       </c>
       <c r="F80">
-        <v>281.034</v>
+        <v>284.637</v>
       </c>
       <c r="G80">
         <v>16</v>
@@ -7847,37 +7847,37 @@
         <v>13.1</v>
       </c>
       <c r="M80">
-        <v>66.2678172</v>
+        <v>67.1174046</v>
       </c>
       <c r="N80">
-        <v>-53.1678172</v>
+        <v>-54.01740460000001</v>
       </c>
       <c r="O80">
-        <v>-11.696919784</v>
+        <v>-11.883829012</v>
       </c>
       <c r="P80">
-        <v>-41.470897416</v>
+        <v>-42.13357558800001</v>
       </c>
       <c r="Q80">
-        <v>-23.070897416</v>
+        <v>-23.73357558800001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1577387157828217</v>
+        <v>0.163069130820099</v>
       </c>
       <c r="T80">
-        <v>2.585189740942766</v>
+        <v>2.708294014320993</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.04349019058982977</v>
+        <v>0.04293968184818636</v>
       </c>
       <c r="W80">
-        <v>0.2255450130589182</v>
+        <v>0.2256748230201976</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1976826844992262</v>
+        <v>0.1951803720372106</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.212527627658177</v>
+        <v>0.214427627658177</v>
       </c>
       <c r="C81">
-        <v>-221.1796515773048</v>
+        <v>-225.3173739312591</v>
       </c>
       <c r="D81">
-        <v>47.45734842269525</v>
+        <v>46.92262606874088</v>
       </c>
       <c r="E81">
-        <v>141.637</v>
+        <v>145.24</v>
       </c>
       <c r="F81">
-        <v>284.637</v>
+        <v>288.24</v>
       </c>
       <c r="G81">
         <v>16</v>
@@ -7929,37 +7929,37 @@
         <v>13.1</v>
       </c>
       <c r="M81">
-        <v>67.1174046</v>
+        <v>67.966992</v>
       </c>
       <c r="N81">
-        <v>-54.01740460000001</v>
+        <v>-54.86699200000001</v>
       </c>
       <c r="O81">
-        <v>-11.883829012</v>
+        <v>-12.07073824</v>
       </c>
       <c r="P81">
-        <v>-42.13357558800001</v>
+        <v>-42.79625376000001</v>
       </c>
       <c r="Q81">
-        <v>-23.73357558800001</v>
+        <v>-24.39625376000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.163069130820099</v>
+        <v>0.1689325873611039</v>
       </c>
       <c r="T81">
-        <v>2.708294014320993</v>
+        <v>2.843708715037042</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.04293968184818636</v>
+        <v>0.04240293582508402</v>
       </c>
       <c r="W81">
-        <v>0.2256748230201976</v>
+        <v>0.2258013877324452</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1951803720372106</v>
+        <v>0.1927406173867455</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.214427627658177</v>
+        <v>0.2163276276581769</v>
       </c>
       <c r="C82">
-        <v>-225.3173739312591</v>
+        <v>-229.4431806503517</v>
       </c>
       <c r="D82">
-        <v>46.92262606874088</v>
+        <v>46.39981934964833</v>
       </c>
       <c r="E82">
-        <v>145.24</v>
+        <v>148.843</v>
       </c>
       <c r="F82">
-        <v>288.24</v>
+        <v>291.843</v>
       </c>
       <c r="G82">
         <v>16</v>
@@ -8011,37 +8011,37 @@
         <v>13.1</v>
       </c>
       <c r="M82">
-        <v>67.966992</v>
+        <v>68.81657940000001</v>
       </c>
       <c r="N82">
-        <v>-54.86699200000001</v>
+        <v>-55.71657940000001</v>
       </c>
       <c r="O82">
-        <v>-12.07073824</v>
+        <v>-12.257647468</v>
       </c>
       <c r="P82">
-        <v>-42.79625376000001</v>
+        <v>-43.45893193200001</v>
       </c>
       <c r="Q82">
-        <v>-24.39625376000001</v>
+        <v>-25.05893193200001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1689325873611039</v>
+        <v>0.1754132498537936</v>
       </c>
       <c r="T82">
-        <v>2.843708715037042</v>
+        <v>2.993377594775834</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.04240293582508402</v>
+        <v>0.04187944279020644</v>
       </c>
       <c r="W82">
-        <v>0.2258013877324452</v>
+        <v>0.2259248273900693</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1927406173867455</v>
+        <v>0.1903611035918474</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2163276276581769</v>
+        <v>0.218227627658177</v>
       </c>
       <c r="C83">
-        <v>-229.4431806503517</v>
+        <v>-233.5574656338643</v>
       </c>
       <c r="D83">
-        <v>46.39981934964833</v>
+        <v>45.88853436613577</v>
       </c>
       <c r="E83">
-        <v>148.843</v>
+        <v>152.446</v>
       </c>
       <c r="F83">
-        <v>291.843</v>
+        <v>295.446</v>
       </c>
       <c r="G83">
         <v>16</v>
@@ -8093,37 +8093,37 @@
         <v>13.1</v>
       </c>
       <c r="M83">
-        <v>68.81657940000001</v>
+        <v>69.66616680000001</v>
       </c>
       <c r="N83">
-        <v>-55.71657940000001</v>
+        <v>-56.56616680000002</v>
       </c>
       <c r="O83">
-        <v>-12.257647468</v>
+        <v>-12.444556696</v>
       </c>
       <c r="P83">
-        <v>-43.45893193200001</v>
+        <v>-44.12161010400001</v>
       </c>
       <c r="Q83">
-        <v>-25.05893193200001</v>
+        <v>-25.72161010400001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1754132498537936</v>
+        <v>0.1826139859567821</v>
       </c>
       <c r="T83">
-        <v>2.993377594775834</v>
+        <v>3.159676350041158</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.04187944279020644</v>
+        <v>0.04136871787813075</v>
       </c>
       <c r="W83">
-        <v>0.2259248273900693</v>
+        <v>0.2260452563243368</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1903611035918474</v>
+        <v>0.1880396267187761</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.218227627658177</v>
+        <v>0.2201276276581769</v>
       </c>
       <c r="C84">
-        <v>-233.5574656338643</v>
+        <v>-237.6606056086171</v>
       </c>
       <c r="D84">
-        <v>45.88853436613577</v>
+        <v>45.38839439138299</v>
       </c>
       <c r="E84">
-        <v>152.446</v>
+        <v>156.049</v>
       </c>
       <c r="F84">
-        <v>295.446</v>
+        <v>299.049</v>
       </c>
       <c r="G84">
         <v>16</v>
@@ -8175,37 +8175,37 @@
         <v>13.1</v>
       </c>
       <c r="M84">
-        <v>69.66616680000001</v>
+        <v>70.51575420000002</v>
       </c>
       <c r="N84">
-        <v>-56.56616680000002</v>
+        <v>-57.41575420000002</v>
       </c>
       <c r="O84">
-        <v>-12.444556696</v>
+        <v>-12.63146592400001</v>
       </c>
       <c r="P84">
-        <v>-44.12161010400001</v>
+        <v>-44.78428827600002</v>
       </c>
       <c r="Q84">
-        <v>-25.72161010400001</v>
+        <v>-26.38428827600002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1826139859567821</v>
+        <v>0.1906618674836517</v>
       </c>
       <c r="T84">
-        <v>3.159676350041158</v>
+        <v>3.345539664749462</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.04136871787813075</v>
+        <v>0.04087029959044242</v>
       </c>
       <c r="W84">
-        <v>0.2260452563243368</v>
+        <v>0.2261627833565737</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1880396267187761</v>
+        <v>0.1857740890474655</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2201276276581769</v>
+        <v>0.222027627658177</v>
       </c>
       <c r="C85">
-        <v>-237.6606056086171</v>
+        <v>-241.7529610546933</v>
       </c>
       <c r="D85">
-        <v>45.38839439138299</v>
+        <v>44.89903894530674</v>
       </c>
       <c r="E85">
-        <v>156.049</v>
+        <v>159.652</v>
       </c>
       <c r="F85">
-        <v>299.049</v>
+        <v>302.652</v>
       </c>
       <c r="G85">
         <v>16</v>
@@ -8257,37 +8257,37 @@
         <v>13.1</v>
       </c>
       <c r="M85">
-        <v>70.51575420000002</v>
+        <v>71.36534160000001</v>
       </c>
       <c r="N85">
-        <v>-57.41575420000002</v>
+        <v>-58.26534160000001</v>
       </c>
       <c r="O85">
-        <v>-12.63146592400001</v>
+        <v>-12.818375152</v>
       </c>
       <c r="P85">
-        <v>-44.78428827600002</v>
+        <v>-45.44696644800001</v>
       </c>
       <c r="Q85">
-        <v>-26.38428827600002</v>
+        <v>-27.04696644800001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1906618674836517</v>
+        <v>0.1997157342013799</v>
       </c>
       <c r="T85">
-        <v>3.345539664749462</v>
+        <v>3.554635893796304</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.04087029959044242</v>
+        <v>0.04038374840484193</v>
       </c>
       <c r="W85">
-        <v>0.2261627833565737</v>
+        <v>0.2262775121261383</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1857740890474655</v>
+        <v>0.1835624927492815</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2220276276581769</v>
+        <v>0.2239276276581769</v>
       </c>
       <c r="C86">
-        <v>-241.7529610546932</v>
+        <v>-245.8348770719199</v>
       </c>
       <c r="D86">
-        <v>44.89903894530682</v>
+        <v>44.42012292808013</v>
       </c>
       <c r="E86">
-        <v>159.652</v>
+        <v>163.255</v>
       </c>
       <c r="F86">
-        <v>302.652</v>
+        <v>306.255</v>
       </c>
       <c r="G86">
         <v>16</v>
@@ -8339,37 +8339,37 @@
         <v>13.1</v>
       </c>
       <c r="M86">
-        <v>71.36534159999999</v>
+        <v>72.214929</v>
       </c>
       <c r="N86">
-        <v>-58.2653416</v>
+        <v>-59.114929</v>
       </c>
       <c r="O86">
-        <v>-12.818375152</v>
+        <v>-13.00528438</v>
       </c>
       <c r="P86">
-        <v>-45.446966448</v>
+        <v>-46.10964462</v>
       </c>
       <c r="Q86">
-        <v>-27.046966448</v>
+        <v>-27.70964462000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1997157342013799</v>
+        <v>0.2099767831481385</v>
       </c>
       <c r="T86">
-        <v>3.554635893796302</v>
+        <v>3.791611620049389</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.04038374840484193</v>
+        <v>0.03990864548243203</v>
       </c>
       <c r="W86">
-        <v>0.2262775121261383</v>
+        <v>0.2263895413952425</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1835624927492815</v>
+        <v>0.1814029340110547</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2239276276581769</v>
+        <v>0.2258276276581769</v>
       </c>
       <c r="C87">
-        <v>-245.8348770719199</v>
+        <v>-249.9066841914782</v>
       </c>
       <c r="D87">
-        <v>44.42012292808013</v>
+        <v>43.95131580852176</v>
       </c>
       <c r="E87">
-        <v>163.255</v>
+        <v>166.858</v>
       </c>
       <c r="F87">
-        <v>306.255</v>
+        <v>309.858</v>
       </c>
       <c r="G87">
         <v>16</v>
@@ -8421,37 +8421,37 @@
         <v>13.1</v>
       </c>
       <c r="M87">
-        <v>72.214929</v>
+        <v>73.0645164</v>
       </c>
       <c r="N87">
-        <v>-59.114929</v>
+        <v>-59.96451640000001</v>
       </c>
       <c r="O87">
-        <v>-13.00528438</v>
+        <v>-13.192193608</v>
       </c>
       <c r="P87">
-        <v>-46.10964462</v>
+        <v>-46.772322792</v>
       </c>
       <c r="Q87">
-        <v>-27.70964462000001</v>
+        <v>-28.37232279200001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2099767831481385</v>
+        <v>0.2217036962301484</v>
       </c>
       <c r="T87">
-        <v>3.791611620049389</v>
+        <v>4.062441021481488</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.03990864548243203</v>
+        <v>0.03944459146519445</v>
       </c>
       <c r="W87">
-        <v>0.2263895413952425</v>
+        <v>0.2264989653325072</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1814029340110547</v>
+        <v>0.1792935975690656</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2258276276581769</v>
+        <v>0.2277276276581769</v>
       </c>
       <c r="C88">
-        <v>-249.9066841914782</v>
+        <v>-253.9686991366579</v>
       </c>
       <c r="D88">
-        <v>43.95131580852176</v>
+        <v>43.49230086334214</v>
       </c>
       <c r="E88">
-        <v>166.858</v>
+        <v>170.461</v>
       </c>
       <c r="F88">
-        <v>309.858</v>
+        <v>313.461</v>
       </c>
       <c r="G88">
         <v>16</v>
@@ -8503,37 +8503,37 @@
         <v>13.1</v>
       </c>
       <c r="M88">
-        <v>73.0645164</v>
+        <v>73.91410380000001</v>
       </c>
       <c r="N88">
-        <v>-59.96451640000001</v>
+        <v>-60.81410380000001</v>
       </c>
       <c r="O88">
-        <v>-13.192193608</v>
+        <v>-13.379102836</v>
       </c>
       <c r="P88">
-        <v>-46.772322792</v>
+        <v>-47.43500096400001</v>
       </c>
       <c r="Q88">
-        <v>-28.37232279200001</v>
+        <v>-29.03500096400001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2217036962301484</v>
+        <v>0.2352347497863136</v>
       </c>
       <c r="T88">
-        <v>4.062441021481488</v>
+        <v>4.374936484672372</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03944459146519445</v>
+        <v>0.0389912053563991</v>
       </c>
       <c r="W88">
-        <v>0.2264989653325072</v>
+        <v>0.2266058737769611</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1792935975690656</v>
+        <v>0.1772327516199959</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2277276276581769</v>
+        <v>0.2296276276581769</v>
       </c>
       <c r="C89">
-        <v>-253.9686991366579</v>
+        <v>-258.0212255364328</v>
       </c>
       <c r="D89">
-        <v>43.49230086334214</v>
+        <v>43.04277446356718</v>
       </c>
       <c r="E89">
-        <v>170.461</v>
+        <v>174.064</v>
       </c>
       <c r="F89">
-        <v>313.461</v>
+        <v>317.064</v>
       </c>
       <c r="G89">
         <v>16</v>
@@ -8585,37 +8585,37 @@
         <v>13.1</v>
       </c>
       <c r="M89">
-        <v>73.91410380000001</v>
+        <v>74.76369120000001</v>
       </c>
       <c r="N89">
-        <v>-60.81410380000001</v>
+        <v>-61.66369120000002</v>
       </c>
       <c r="O89">
-        <v>-13.379102836</v>
+        <v>-13.566012064</v>
       </c>
       <c r="P89">
-        <v>-47.43500096400001</v>
+        <v>-48.09767913600001</v>
       </c>
       <c r="Q89">
-        <v>-29.03500096400001</v>
+        <v>-29.69767913600001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2352347497863136</v>
+        <v>0.2510209789351731</v>
       </c>
       <c r="T89">
-        <v>4.374936484672372</v>
+        <v>4.739514525061736</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.0389912053563991</v>
+        <v>0.03854812347734911</v>
       </c>
       <c r="W89">
-        <v>0.2266058737769611</v>
+        <v>0.2267103524840411</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1772327516199959</v>
+        <v>0.1752187430788595</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2296276276581769</v>
+        <v>0.2315276276581769</v>
       </c>
       <c r="C90">
-        <v>-258.0212255364328</v>
+        <v>-262.0645545952377</v>
       </c>
       <c r="D90">
-        <v>43.04277446356718</v>
+        <v>42.60244540476231</v>
       </c>
       <c r="E90">
-        <v>174.064</v>
+        <v>177.667</v>
       </c>
       <c r="F90">
-        <v>317.064</v>
+        <v>320.667</v>
       </c>
       <c r="G90">
         <v>16</v>
@@ -8667,37 +8667,37 @@
         <v>13.1</v>
       </c>
       <c r="M90">
-        <v>74.76369120000001</v>
+        <v>75.61327860000002</v>
       </c>
       <c r="N90">
-        <v>-61.66369120000002</v>
+        <v>-62.51327860000002</v>
       </c>
       <c r="O90">
-        <v>-13.566012064</v>
+        <v>-13.75292129200001</v>
       </c>
       <c r="P90">
-        <v>-48.09767913600001</v>
+        <v>-48.76035730800002</v>
       </c>
       <c r="Q90">
-        <v>-29.69767913600001</v>
+        <v>-30.36035730800002</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2510209789351731</v>
+        <v>0.2696774315656434</v>
       </c>
       <c r="T90">
-        <v>4.739514525061736</v>
+        <v>5.170379481885531</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.03854812347734911</v>
+        <v>0.03811499849445755</v>
       </c>
       <c r="W90">
-        <v>0.2267103524840411</v>
+        <v>0.2268124833550069</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1752187430788595</v>
+        <v>0.1732499931566251</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2315276276581769</v>
+        <v>0.2334276276581769</v>
       </c>
       <c r="C91">
-        <v>-262.0645545952377</v>
+        <v>-266.0989657220496</v>
       </c>
       <c r="D91">
-        <v>42.60244540476231</v>
+        <v>42.17103427795044</v>
       </c>
       <c r="E91">
-        <v>177.667</v>
+        <v>181.27</v>
       </c>
       <c r="F91">
-        <v>320.667</v>
+        <v>324.27</v>
       </c>
       <c r="G91">
         <v>16</v>
@@ -8749,37 +8749,37 @@
         <v>13.1</v>
       </c>
       <c r="M91">
-        <v>75.61327860000002</v>
+        <v>76.46286600000001</v>
       </c>
       <c r="N91">
-        <v>-62.51327860000002</v>
+        <v>-63.36286600000001</v>
       </c>
       <c r="O91">
-        <v>-13.75292129200001</v>
+        <v>-13.93983052</v>
       </c>
       <c r="P91">
-        <v>-48.76035730800002</v>
+        <v>-49.42303548000001</v>
       </c>
       <c r="Q91">
-        <v>-30.36035730800002</v>
+        <v>-31.02303548000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2696774315656434</v>
+        <v>0.2920651747222078</v>
       </c>
       <c r="T91">
-        <v>5.170379481885531</v>
+        <v>5.687417430074084</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.03811499849445755</v>
+        <v>0.0376914985111858</v>
       </c>
       <c r="W91">
-        <v>0.2268124833550069</v>
+        <v>0.2269123446510624</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1732499931566251</v>
+        <v>0.1713249932326627</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2334276276581769</v>
+        <v>0.2353276276581769</v>
       </c>
       <c r="C92">
-        <v>-266.0989657220496</v>
+        <v>-270.1247271216309</v>
       </c>
       <c r="D92">
-        <v>42.17103427795044</v>
+        <v>41.74827287836908</v>
       </c>
       <c r="E92">
-        <v>181.27</v>
+        <v>184.873</v>
       </c>
       <c r="F92">
-        <v>324.27</v>
+        <v>327.873</v>
       </c>
       <c r="G92">
         <v>16</v>
@@ -8831,37 +8831,37 @@
         <v>13.1</v>
       </c>
       <c r="M92">
-        <v>76.46286600000001</v>
+        <v>77.31245340000001</v>
       </c>
       <c r="N92">
-        <v>-63.36286600000001</v>
+        <v>-64.21245340000002</v>
       </c>
       <c r="O92">
-        <v>-13.93983052</v>
+        <v>-14.126739748</v>
       </c>
       <c r="P92">
-        <v>-49.42303548000001</v>
+        <v>-50.08571365200001</v>
       </c>
       <c r="Q92">
-        <v>-31.02303548000001</v>
+        <v>-31.68571365200001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2920651747222078</v>
+        <v>0.3194279719135643</v>
       </c>
       <c r="T92">
-        <v>5.687417430074084</v>
+        <v>6.319352700082317</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.0376914985111858</v>
+        <v>0.03727730621985408</v>
       </c>
       <c r="W92">
-        <v>0.2269123446510624</v>
+        <v>0.2270100111933584</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1713249932326627</v>
+        <v>0.1694423009993367</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2353276276581769</v>
+        <v>0.237227627658177</v>
       </c>
       <c r="C93">
-        <v>-270.1247271216309</v>
+        <v>-274.1420963505624</v>
       </c>
       <c r="D93">
-        <v>41.74827287836908</v>
+        <v>41.33390364943761</v>
       </c>
       <c r="E93">
-        <v>184.873</v>
+        <v>188.476</v>
       </c>
       <c r="F93">
-        <v>327.873</v>
+        <v>331.476</v>
       </c>
       <c r="G93">
         <v>16</v>
@@ -8913,37 +8913,37 @@
         <v>13.1</v>
       </c>
       <c r="M93">
-        <v>77.31245340000001</v>
+        <v>78.1620408</v>
       </c>
       <c r="N93">
-        <v>-64.21245340000002</v>
+        <v>-65.06204080000001</v>
       </c>
       <c r="O93">
-        <v>-14.126739748</v>
+        <v>-14.313648976</v>
       </c>
       <c r="P93">
-        <v>-50.08571365200001</v>
+        <v>-50.748391824</v>
       </c>
       <c r="Q93">
-        <v>-31.68571365200001</v>
+        <v>-32.348391824</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3194279719135643</v>
+        <v>0.3536314684027599</v>
       </c>
       <c r="T93">
-        <v>6.319352700082317</v>
+        <v>7.109271787592609</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03727730621985408</v>
+        <v>0.03687211810876872</v>
       </c>
       <c r="W93">
-        <v>0.2270100111933584</v>
+        <v>0.2271055545499523</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1694423009993367</v>
+        <v>0.1676005368580396</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.237227627658177</v>
+        <v>0.239127627658177</v>
       </c>
       <c r="C94">
-        <v>-274.1420963505624</v>
+        <v>-278.1513208404878</v>
       </c>
       <c r="D94">
-        <v>41.33390364943761</v>
+        <v>40.92767915951219</v>
       </c>
       <c r="E94">
-        <v>188.476</v>
+        <v>192.079</v>
       </c>
       <c r="F94">
-        <v>331.476</v>
+        <v>335.079</v>
       </c>
       <c r="G94">
         <v>16</v>
@@ -8995,37 +8995,37 @@
         <v>13.1</v>
       </c>
       <c r="M94">
-        <v>78.1620408</v>
+        <v>79.0116282</v>
       </c>
       <c r="N94">
-        <v>-65.06204080000001</v>
+        <v>-65.91162820000001</v>
       </c>
       <c r="O94">
-        <v>-14.313648976</v>
+        <v>-14.500558204</v>
       </c>
       <c r="P94">
-        <v>-50.748391824</v>
+        <v>-51.41106999600001</v>
       </c>
       <c r="Q94">
-        <v>-32.348391824</v>
+        <v>-33.01106999600001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3536314684027599</v>
+        <v>0.3976073924602971</v>
       </c>
       <c r="T94">
-        <v>7.109271787592609</v>
+        <v>8.124882042962982</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03687211810876872</v>
+        <v>0.03647564372050239</v>
       </c>
       <c r="W94">
-        <v>0.2271055545499523</v>
+        <v>0.2271990432107056</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1676005368580396</v>
+        <v>0.1657983805477381</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.239127627658177</v>
+        <v>0.241027627658177</v>
       </c>
       <c r="C95">
-        <v>-278.1513208404878</v>
+        <v>-282.1526383908051</v>
       </c>
       <c r="D95">
-        <v>40.92767915951219</v>
+        <v>40.5293616091949</v>
       </c>
       <c r="E95">
-        <v>192.079</v>
+        <v>195.682</v>
       </c>
       <c r="F95">
-        <v>335.079</v>
+        <v>338.682</v>
       </c>
       <c r="G95">
         <v>16</v>
@@ -9077,37 +9077,37 @@
         <v>13.1</v>
       </c>
       <c r="M95">
-        <v>79.0116282</v>
+        <v>79.86121560000001</v>
       </c>
       <c r="N95">
-        <v>-65.91162820000001</v>
+        <v>-66.76121560000001</v>
       </c>
       <c r="O95">
-        <v>-14.500558204</v>
+        <v>-14.687467432</v>
       </c>
       <c r="P95">
-        <v>-51.41106999600001</v>
+        <v>-52.07374816800001</v>
       </c>
       <c r="Q95">
-        <v>-33.01106999600001</v>
+        <v>-33.67374816800001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3976073924602971</v>
+        <v>0.4562419578703467</v>
       </c>
       <c r="T95">
-        <v>8.124882042962982</v>
+        <v>9.479029050123483</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03647564372050239</v>
+        <v>0.03608760495751832</v>
       </c>
       <c r="W95">
-        <v>0.2271990432107056</v>
+        <v>0.2272905427510172</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1657983805477381</v>
+        <v>0.1640345679887196</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.241027627658177</v>
+        <v>0.2429276276581769</v>
       </c>
       <c r="C96">
-        <v>-282.1526383908051</v>
+        <v>-286.1462776328651</v>
       </c>
       <c r="D96">
-        <v>40.5293616091949</v>
+        <v>40.13872236713487</v>
       </c>
       <c r="E96">
-        <v>195.682</v>
+        <v>199.285</v>
       </c>
       <c r="F96">
-        <v>338.682</v>
+        <v>342.285</v>
       </c>
       <c r="G96">
         <v>16</v>
@@ -9159,37 +9159,37 @@
         <v>13.1</v>
       </c>
       <c r="M96">
-        <v>79.86121560000001</v>
+        <v>80.71080300000001</v>
       </c>
       <c r="N96">
-        <v>-66.76121560000001</v>
+        <v>-67.61080300000002</v>
       </c>
       <c r="O96">
-        <v>-14.687467432</v>
+        <v>-14.87437666</v>
       </c>
       <c r="P96">
-        <v>-52.07374816800001</v>
+        <v>-52.73642634000002</v>
       </c>
       <c r="Q96">
-        <v>-33.67374816800001</v>
+        <v>-34.33642634000002</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4562419578703467</v>
+        <v>0.5383303494444162</v>
       </c>
       <c r="T96">
-        <v>9.479029050123483</v>
+        <v>11.37483486014818</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03608760495751832</v>
+        <v>0.0357077354316497</v>
       </c>
       <c r="W96">
-        <v>0.2272905427510172</v>
+        <v>0.227380115985217</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1640345679887196</v>
+        <v>0.1623078883256804</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2429276276581769</v>
+        <v>0.2448276276581769</v>
       </c>
       <c r="C97">
-        <v>-286.1462776328651</v>
+        <v>-290.1324584675809</v>
       </c>
       <c r="D97">
-        <v>40.13872236713487</v>
+        <v>39.75554153241913</v>
       </c>
       <c r="E97">
-        <v>199.285</v>
+        <v>202.888</v>
       </c>
       <c r="F97">
-        <v>342.285</v>
+        <v>345.888</v>
       </c>
       <c r="G97">
         <v>16</v>
@@ -9241,37 +9241,37 @@
         <v>13.1</v>
       </c>
       <c r="M97">
-        <v>80.71080300000001</v>
+        <v>81.56039040000002</v>
       </c>
       <c r="N97">
-        <v>-67.61080300000002</v>
+        <v>-68.46039040000002</v>
       </c>
       <c r="O97">
-        <v>-14.87437666</v>
+        <v>-15.06128588800001</v>
       </c>
       <c r="P97">
-        <v>-52.73642634000002</v>
+        <v>-53.39910451200002</v>
       </c>
       <c r="Q97">
-        <v>-34.33642634000002</v>
+        <v>-34.99910451200002</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5383303494444162</v>
+        <v>0.6614629368055206</v>
       </c>
       <c r="T97">
-        <v>11.37483486014818</v>
+        <v>14.21854357518524</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.0357077354316497</v>
+        <v>0.03533577985423669</v>
       </c>
       <c r="W97">
-        <v>0.227380115985217</v>
+        <v>0.227467823110371</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1623078883256804</v>
+        <v>0.1606171811556213</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2448276276581769</v>
+        <v>0.2467276276581769</v>
       </c>
       <c r="C98">
-        <v>-290.1324584675808</v>
+        <v>-294.1113924782093</v>
       </c>
       <c r="D98">
-        <v>39.75554153241917</v>
+        <v>39.37960752179071</v>
       </c>
       <c r="E98">
-        <v>202.888</v>
+        <v>206.491</v>
       </c>
       <c r="F98">
-        <v>345.888</v>
+        <v>349.491</v>
       </c>
       <c r="G98">
         <v>16</v>
@@ -9323,37 +9323,37 @@
         <v>13.1</v>
       </c>
       <c r="M98">
-        <v>81.5603904</v>
+        <v>82.40997779999999</v>
       </c>
       <c r="N98">
-        <v>-68.46039040000001</v>
+        <v>-69.3099778</v>
       </c>
       <c r="O98">
-        <v>-15.061285888</v>
+        <v>-15.248195116</v>
       </c>
       <c r="P98">
-        <v>-53.39910451200001</v>
+        <v>-54.061782684</v>
       </c>
       <c r="Q98">
-        <v>-34.99910451200001</v>
+        <v>-35.661782684</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6614629368055189</v>
+        <v>0.8666839157406917</v>
       </c>
       <c r="T98">
-        <v>14.2185435751852</v>
+        <v>18.95805810024693</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.03533577985423669</v>
+        <v>0.03497149346398683</v>
       </c>
       <c r="W98">
-        <v>0.227467823110371</v>
+        <v>0.2275537218411919</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1606171811556213</v>
+        <v>0.1589613339272128</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2467276276581769</v>
+        <v>0.2486276276581769</v>
       </c>
       <c r="C99">
-        <v>-294.1113924782093</v>
+        <v>-298.0832833199318</v>
       </c>
       <c r="D99">
-        <v>39.37960752179071</v>
+        <v>39.01071668006825</v>
       </c>
       <c r="E99">
-        <v>206.491</v>
+        <v>210.094</v>
       </c>
       <c r="F99">
-        <v>349.491</v>
+        <v>353.094</v>
       </c>
       <c r="G99">
         <v>16</v>
@@ -9405,37 +9405,37 @@
         <v>13.1</v>
       </c>
       <c r="M99">
-        <v>82.40997779999999</v>
+        <v>83.2595652</v>
       </c>
       <c r="N99">
-        <v>-69.3099778</v>
+        <v>-70.1595652</v>
       </c>
       <c r="O99">
-        <v>-15.248195116</v>
+        <v>-15.435104344</v>
       </c>
       <c r="P99">
-        <v>-54.061782684</v>
+        <v>-54.724460856</v>
       </c>
       <c r="Q99">
-        <v>-35.661782684</v>
+        <v>-36.324460856</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.8666839157406917</v>
+        <v>1.277125873611038</v>
       </c>
       <c r="T99">
-        <v>18.95805810024693</v>
+        <v>28.4370871503704</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.03497149346398683</v>
+        <v>0.03461464148986451</v>
       </c>
       <c r="W99">
-        <v>0.2275537218411919</v>
+        <v>0.22763786753669</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1589613339272128</v>
+        <v>0.1573392794993841</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2486276276581769</v>
+        <v>0.2505276276581769</v>
       </c>
       <c r="C100">
-        <v>-298.0832833199318</v>
+        <v>-302.0483270877417</v>
       </c>
       <c r="D100">
-        <v>39.01071668006825</v>
+        <v>38.64867291225838</v>
       </c>
       <c r="E100">
-        <v>210.094</v>
+        <v>213.697</v>
       </c>
       <c r="F100">
-        <v>353.094</v>
+        <v>356.697</v>
       </c>
       <c r="G100">
         <v>16</v>
@@ -9487,37 +9487,37 @@
         <v>13.1</v>
       </c>
       <c r="M100">
-        <v>83.2595652</v>
+        <v>84.1091526</v>
       </c>
       <c r="N100">
-        <v>-70.1595652</v>
+        <v>-71.00915260000001</v>
       </c>
       <c r="O100">
-        <v>-15.435104344</v>
+        <v>-15.622013572</v>
       </c>
       <c r="P100">
-        <v>-54.724460856</v>
+        <v>-55.38713902800001</v>
       </c>
       <c r="Q100">
-        <v>-36.324460856</v>
+        <v>-36.98713902800001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.277125873611038</v>
+        <v>2.508451747222076</v>
       </c>
       <c r="T100">
-        <v>28.4370871503704</v>
+        <v>56.87417430074079</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.03461464148986451</v>
+        <v>0.03426499864653255</v>
       </c>
       <c r="W100">
-        <v>0.22763786753669</v>
+        <v>0.2277203133191476</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1573392794993841</v>
+        <v>0.1557499938478751</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2505276276581769</v>
-      </c>
-      <c r="C101">
-        <v>-302.0483270877417</v>
-      </c>
-      <c r="D101">
-        <v>38.64867291225838</v>
-      </c>
-      <c r="E101">
-        <v>213.697</v>
-      </c>
-      <c r="F101">
-        <v>356.697</v>
-      </c>
-      <c r="G101">
-        <v>16</v>
-      </c>
-      <c r="H101">
-        <v>217.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>31.5</v>
-      </c>
-      <c r="K101">
-        <v>18.4</v>
-      </c>
-      <c r="L101">
-        <v>13.1</v>
-      </c>
-      <c r="M101">
-        <v>84.1091526</v>
-      </c>
-      <c r="N101">
-        <v>-71.00915260000001</v>
-      </c>
-      <c r="O101">
-        <v>-15.622013572</v>
-      </c>
-      <c r="P101">
-        <v>-55.38713902800001</v>
-      </c>
-      <c r="Q101">
-        <v>-36.98713902800001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.508451747222076</v>
-      </c>
-      <c r="T101">
-        <v>56.87417430074079</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.03426499864653255</v>
-      </c>
-      <c r="W101">
-        <v>0.2277203133191476</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1557499938478751</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
